--- a/combination_frequency_summary.xlsx
+++ b/combination_frequency_summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E985"/>
+  <dimension ref="A1:F985"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,6 +454,11 @@
           <t>avg_amount_per_case</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>total_item_quantity</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -475,6 +480,9 @@
       <c r="E2" t="n">
         <v>1790.078035294118</v>
       </c>
+      <c r="F2" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -496,6 +504,9 @@
       <c r="E3" t="n">
         <v>1979.367510344828</v>
       </c>
+      <c r="F3" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -517,6 +528,9 @@
       <c r="E4" t="n">
         <v>2857.105098039216</v>
       </c>
+      <c r="F4" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -538,6 +552,9 @@
       <c r="E5" t="n">
         <v>2226.376593548387</v>
       </c>
+      <c r="F5" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -559,6 +576,9 @@
       <c r="E6" t="n">
         <v>1289.82</v>
       </c>
+      <c r="F6" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -580,6 +600,9 @@
       <c r="E7" t="n">
         <v>1152.47</v>
       </c>
+      <c r="F7" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -601,6 +624,9 @@
       <c r="E8" t="n">
         <v>1123.319525925926</v>
       </c>
+      <c r="F8" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -622,6 +648,9 @@
       <c r="E9" t="n">
         <v>3622.986685714286</v>
       </c>
+      <c r="F9" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -643,6 +672,9 @@
       <c r="E10" t="n">
         <v>2029.27066</v>
       </c>
+      <c r="F10" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -664,6 +696,9 @@
       <c r="E11" t="n">
         <v>2025.356975</v>
       </c>
+      <c r="F11" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -685,6 +720,9 @@
       <c r="E12" t="n">
         <v>2552.842494736842</v>
       </c>
+      <c r="F12" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -706,6 +744,9 @@
       <c r="E13" t="n">
         <v>2987.224782352941</v>
       </c>
+      <c r="F13" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -727,6 +768,9 @@
       <c r="E14" t="n">
         <v>2500.231607142857</v>
       </c>
+      <c r="F14" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -748,6 +792,9 @@
       <c r="E15" t="n">
         <v>2638.298769230769</v>
       </c>
+      <c r="F15" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -769,6 +816,9 @@
       <c r="E16" t="n">
         <v>2702.494146153846</v>
       </c>
+      <c r="F16" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -790,6 +840,9 @@
       <c r="E17" t="n">
         <v>2105.210933333333</v>
       </c>
+      <c r="F17" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -811,6 +864,9 @@
       <c r="E18" t="n">
         <v>2480.85</v>
       </c>
+      <c r="F18" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -832,6 +888,9 @@
       <c r="E19" t="n">
         <v>2418.600454545454</v>
       </c>
+      <c r="F19" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -853,6 +912,9 @@
       <c r="E20" t="n">
         <v>2487.61365</v>
       </c>
+      <c r="F20" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -874,6 +936,9 @@
       <c r="E21" t="n">
         <v>2220.83</v>
       </c>
+      <c r="F21" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -895,6 +960,9 @@
       <c r="E22" t="n">
         <v>2009.39349</v>
       </c>
+      <c r="F22" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -916,6 +984,9 @@
       <c r="E23" t="n">
         <v>3014.064033333334</v>
       </c>
+      <c r="F23" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -937,6 +1008,9 @@
       <c r="E24" t="n">
         <v>3053.200911111111</v>
       </c>
+      <c r="F24" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -958,6 +1032,9 @@
       <c r="E25" t="n">
         <v>2541.330166666667</v>
       </c>
+      <c r="F25" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -979,6 +1056,9 @@
       <c r="E26" t="n">
         <v>1798.474666666667</v>
       </c>
+      <c r="F26" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1000,6 +1080,9 @@
       <c r="E27" t="n">
         <v>1117.45</v>
       </c>
+      <c r="F27" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1021,6 +1104,9 @@
       <c r="E28" t="n">
         <v>2750.84605</v>
       </c>
+      <c r="F28" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1042,6 +1128,9 @@
       <c r="E29" t="n">
         <v>2648.358657142857</v>
       </c>
+      <c r="F29" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1063,6 +1152,9 @@
       <c r="E30" t="n">
         <v>1859.9</v>
       </c>
+      <c r="F30" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1084,6 +1176,9 @@
       <c r="E31" t="n">
         <v>2418.072057142857</v>
       </c>
+      <c r="F31" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1105,6 +1200,9 @@
       <c r="E32" t="n">
         <v>1961.092657142857</v>
       </c>
+      <c r="F32" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1126,6 +1224,9 @@
       <c r="E33" t="n">
         <v>2993.6531</v>
       </c>
+      <c r="F33" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1147,6 +1248,9 @@
       <c r="E34" t="n">
         <v>1677.619914285714</v>
       </c>
+      <c r="F34" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1168,6 +1272,9 @@
       <c r="E35" t="n">
         <v>2101.933316666667</v>
       </c>
+      <c r="F35" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1189,6 +1296,9 @@
       <c r="E36" t="n">
         <v>1681.892333333333</v>
       </c>
+      <c r="F36" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1210,6 +1320,9 @@
       <c r="E37" t="n">
         <v>2076.93295</v>
       </c>
+      <c r="F37" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1231,6 +1344,9 @@
       <c r="E38" t="n">
         <v>2174.0642</v>
       </c>
+      <c r="F38" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1252,6 +1368,9 @@
       <c r="E39" t="n">
         <v>2261.447766666667</v>
       </c>
+      <c r="F39" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1273,6 +1392,9 @@
       <c r="E40" t="n">
         <v>3746.939033333334</v>
       </c>
+      <c r="F40" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1294,6 +1416,9 @@
       <c r="E41" t="n">
         <v>2040.732733333333</v>
       </c>
+      <c r="F41" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1315,6 +1440,9 @@
       <c r="E42" t="n">
         <v>1298.1081</v>
       </c>
+      <c r="F42" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1336,6 +1464,9 @@
       <c r="E43" t="n">
         <v>2134.154266666667</v>
       </c>
+      <c r="F43" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1357,6 +1488,9 @@
       <c r="E44" t="n">
         <v>2252.893566666667</v>
       </c>
+      <c r="F44" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1378,6 +1512,9 @@
       <c r="E45" t="n">
         <v>2737.656483333334</v>
       </c>
+      <c r="F45" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1399,6 +1536,9 @@
       <c r="E46" t="n">
         <v>2719.11555</v>
       </c>
+      <c r="F46" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1420,6 +1560,9 @@
       <c r="E47" t="n">
         <v>2279.7357</v>
       </c>
+      <c r="F47" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1441,6 +1584,9 @@
       <c r="E48" t="n">
         <v>2042.696</v>
       </c>
+      <c r="F48" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1462,6 +1608,9 @@
       <c r="E49" t="n">
         <v>3674.26544</v>
       </c>
+      <c r="F49" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1483,6 +1632,9 @@
       <c r="E50" t="n">
         <v>2916.77036</v>
       </c>
+      <c r="F50" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1504,6 +1656,9 @@
       <c r="E51" t="n">
         <v>3011.93438</v>
       </c>
+      <c r="F51" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1525,6 +1680,9 @@
       <c r="E52" t="n">
         <v>1457.4404</v>
       </c>
+      <c r="F52" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1546,6 +1704,9 @@
       <c r="E53" t="n">
         <v>3243.33252</v>
       </c>
+      <c r="F53" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1567,6 +1728,9 @@
       <c r="E54" t="n">
         <v>2849.89408</v>
       </c>
+      <c r="F54" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1588,6 +1752,9 @@
       <c r="E55" t="n">
         <v>1289.82</v>
       </c>
+      <c r="F55" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1609,6 +1776,9 @@
       <c r="E56" t="n">
         <v>2394.16494</v>
       </c>
+      <c r="F56" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1630,6 +1800,9 @@
       <c r="E57" t="n">
         <v>3179.85364</v>
       </c>
+      <c r="F57" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1651,6 +1824,9 @@
       <c r="E58" t="n">
         <v>1941.44045</v>
       </c>
+      <c r="F58" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1672,6 +1848,9 @@
       <c r="E59" t="n">
         <v>1784.9</v>
       </c>
+      <c r="F59" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1693,6 +1872,9 @@
       <c r="E60" t="n">
         <v>2418.6574</v>
       </c>
+      <c r="F60" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1714,6 +1896,9 @@
       <c r="E61" t="n">
         <v>1468.6</v>
       </c>
+      <c r="F61" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1735,6 +1920,9 @@
       <c r="E62" t="n">
         <v>2490.044175</v>
       </c>
+      <c r="F62" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1756,6 +1944,9 @@
       <c r="E63" t="n">
         <v>1775.33945</v>
       </c>
+      <c r="F63" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1777,6 +1968,9 @@
       <c r="E64" t="n">
         <v>3181.97465</v>
       </c>
+      <c r="F64" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1798,6 +1992,9 @@
       <c r="E65" t="n">
         <v>2402.0192</v>
       </c>
+      <c r="F65" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1819,6 +2016,9 @@
       <c r="E66" t="n">
         <v>1740.58975</v>
       </c>
+      <c r="F66" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1840,6 +2040,9 @@
       <c r="E67" t="n">
         <v>1128.56115</v>
       </c>
+      <c r="F67" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1861,6 +2064,9 @@
       <c r="E68" t="n">
         <v>2447.45</v>
       </c>
+      <c r="F68" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1882,6 +2088,9 @@
       <c r="E69" t="n">
         <v>2931.3835</v>
       </c>
+      <c r="F69" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1903,6 +2112,9 @@
       <c r="E70" t="n">
         <v>3029.604375</v>
       </c>
+      <c r="F70" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1924,6 +2136,9 @@
       <c r="E71" t="n">
         <v>2637.525275</v>
       </c>
+      <c r="F71" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1945,6 +2160,9 @@
       <c r="E72" t="n">
         <v>1951.9246</v>
       </c>
+      <c r="F72" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -1966,6 +2184,9 @@
       <c r="E73" t="n">
         <v>1124</v>
       </c>
+      <c r="F73" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1987,6 +2208,9 @@
       <c r="E74" t="n">
         <v>2278.4136</v>
       </c>
+      <c r="F74" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2008,6 +2232,9 @@
       <c r="E75" t="n">
         <v>2543.562233333334</v>
       </c>
+      <c r="F75" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2029,6 +2256,9 @@
       <c r="E76" t="n">
         <v>2484.838633333333</v>
       </c>
+      <c r="F76" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2050,6 +2280,9 @@
       <c r="E77" t="n">
         <v>2410.4747</v>
       </c>
+      <c r="F77" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2071,6 +2304,9 @@
       <c r="E78" t="n">
         <v>1816.771533333333</v>
       </c>
+      <c r="F78" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2092,6 +2328,9 @@
       <c r="E79" t="n">
         <v>4000.393066666667</v>
       </c>
+      <c r="F79" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2113,6 +2352,9 @@
       <c r="E80" t="n">
         <v>80</v>
       </c>
+      <c r="F80" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2134,6 +2376,9 @@
       <c r="E81" t="n">
         <v>1117.45</v>
       </c>
+      <c r="F81" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2155,6 +2400,9 @@
       <c r="E82" t="n">
         <v>1916.227533333333</v>
       </c>
+      <c r="F82" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2176,6 +2424,9 @@
       <c r="E83" t="n">
         <v>3205.4449</v>
       </c>
+      <c r="F83" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2197,6 +2448,9 @@
       <c r="E84" t="n">
         <v>2505.112766666667</v>
       </c>
+      <c r="F84" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2218,6 +2472,9 @@
       <c r="E85" t="n">
         <v>2303.2704</v>
       </c>
+      <c r="F85" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2239,6 +2496,9 @@
       <c r="E86" t="n">
         <v>3828.770966666667</v>
       </c>
+      <c r="F86" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2260,6 +2520,9 @@
       <c r="E87" t="n">
         <v>2208.3902</v>
       </c>
+      <c r="F87" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2281,6 +2544,9 @@
       <c r="E88" t="n">
         <v>2293.7577</v>
       </c>
+      <c r="F88" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2302,6 +2568,9 @@
       <c r="E89" t="n">
         <v>3040.087466666666</v>
       </c>
+      <c r="F89" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2323,6 +2592,9 @@
       <c r="E90" t="n">
         <v>2236.9538</v>
       </c>
+      <c r="F90" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2344,6 +2616,9 @@
       <c r="E91" t="n">
         <v>3393.333766666667</v>
       </c>
+      <c r="F91" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -2365,6 +2640,9 @@
       <c r="E92" t="n">
         <v>892.4500000000002</v>
       </c>
+      <c r="F92" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2386,6 +2664,9 @@
       <c r="E93" t="n">
         <v>2630.85</v>
       </c>
+      <c r="F93" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2407,6 +2688,9 @@
       <c r="E94" t="n">
         <v>2705.85</v>
       </c>
+      <c r="F94" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2428,6 +2712,9 @@
       <c r="E95" t="n">
         <v>2020.534733333333</v>
       </c>
+      <c r="F95" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -2449,6 +2736,9 @@
       <c r="E96" t="n">
         <v>2018.034466666667</v>
       </c>
+      <c r="F96" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -2470,6 +2760,9 @@
       <c r="E97" t="n">
         <v>2477.218266666667</v>
       </c>
+      <c r="F97" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -2491,6 +2784,9 @@
       <c r="E98" t="n">
         <v>2398.9143</v>
       </c>
+      <c r="F98" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -2512,6 +2808,9 @@
       <c r="E99" t="n">
         <v>4326.4754</v>
       </c>
+      <c r="F99" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -2533,6 +2832,9 @@
       <c r="E100" t="n">
         <v>3571.328466666667</v>
       </c>
+      <c r="F100" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -2554,6 +2856,9 @@
       <c r="E101" t="n">
         <v>2626.376033333333</v>
       </c>
+      <c r="F101" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -2575,6 +2880,9 @@
       <c r="E102" t="n">
         <v>3925.439766666666</v>
       </c>
+      <c r="F102" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -2596,6 +2904,9 @@
       <c r="E103" t="n">
         <v>2424.113233333333</v>
       </c>
+      <c r="F103" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -2617,6 +2928,9 @@
       <c r="E104" t="n">
         <v>3077.7145</v>
       </c>
+      <c r="F104" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -2638,6 +2952,9 @@
       <c r="E105" t="n">
         <v>2792.642600000001</v>
       </c>
+      <c r="F105" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -2659,6 +2976,9 @@
       <c r="E106" t="n">
         <v>2280.428466666667</v>
       </c>
+      <c r="F106" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -2680,6 +3000,9 @@
       <c r="E107" t="n">
         <v>2221.83</v>
       </c>
+      <c r="F107" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -2701,6 +3024,9 @@
       <c r="E108" t="n">
         <v>1152.47</v>
       </c>
+      <c r="F108" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -2722,6 +3048,9 @@
       <c r="E109" t="n">
         <v>1152.47</v>
       </c>
+      <c r="F109" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -2743,6 +3072,9 @@
       <c r="E110" t="n">
         <v>2850.5344</v>
       </c>
+      <c r="F110" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -2764,6 +3096,9 @@
       <c r="E111" t="n">
         <v>2759.353233333333</v>
       </c>
+      <c r="F111" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -2785,6 +3120,9 @@
       <c r="E112" t="n">
         <v>2782.1342</v>
       </c>
+      <c r="F112" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -2806,6 +3144,9 @@
       <c r="E113" t="n">
         <v>2547.738266666667</v>
       </c>
+      <c r="F113" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -2827,6 +3168,9 @@
       <c r="E114" t="n">
         <v>1635</v>
       </c>
+      <c r="F114" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -2848,6 +3192,9 @@
       <c r="E115" t="n">
         <v>2308.1132</v>
       </c>
+      <c r="F115" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -2869,6 +3216,9 @@
       <c r="E116" t="n">
         <v>1785.107933333333</v>
       </c>
+      <c r="F116" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -2890,6 +3240,9 @@
       <c r="E117" t="n">
         <v>1117.45</v>
       </c>
+      <c r="F117" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -2911,6 +3264,9 @@
       <c r="E118" t="n">
         <v>1131.6411</v>
       </c>
+      <c r="F118" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -2932,6 +3288,9 @@
       <c r="E119" t="n">
         <v>2423.8</v>
       </c>
+      <c r="F119" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -2953,6 +3312,9 @@
       <c r="E120" t="n">
         <v>1879.93345</v>
       </c>
+      <c r="F120" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -2974,6 +3336,9 @@
       <c r="E121" t="n">
         <v>150</v>
       </c>
+      <c r="F121" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -2995,6 +3360,9 @@
       <c r="E122" t="n">
         <v>1765.1167</v>
       </c>
+      <c r="F122" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -3016,6 +3384,9 @@
       <c r="E123" t="n">
         <v>1777.2738</v>
       </c>
+      <c r="F123" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -3037,6 +3408,9 @@
       <c r="E124" t="n">
         <v>1970.5288</v>
       </c>
+      <c r="F124" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -3058,6 +3432,9 @@
       <c r="E125" t="n">
         <v>2744.3514</v>
       </c>
+      <c r="F125" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -3079,6 +3456,9 @@
       <c r="E126" t="n">
         <v>1804.625</v>
       </c>
+      <c r="F126" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -3100,6 +3480,9 @@
       <c r="E127" t="n">
         <v>2721.73395</v>
       </c>
+      <c r="F127" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -3121,6 +3504,9 @@
       <c r="E128" t="n">
         <v>3280.8239</v>
       </c>
+      <c r="F128" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -3142,6 +3528,9 @@
       <c r="E129" t="n">
         <v>4272.6668</v>
       </c>
+      <c r="F129" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -3163,6 +3552,9 @@
       <c r="E130" t="n">
         <v>1765.8289</v>
       </c>
+      <c r="F130" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -3184,6 +3576,9 @@
       <c r="E131" t="n">
         <v>2032.183</v>
       </c>
+      <c r="F131" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -3205,6 +3600,9 @@
       <c r="E132" t="n">
         <v>3381.4932</v>
       </c>
+      <c r="F132" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -3226,6 +3624,9 @@
       <c r="E133" t="n">
         <v>2786.22835</v>
       </c>
+      <c r="F133" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -3247,6 +3648,9 @@
       <c r="E134" t="n">
         <v>2714.403600000001</v>
       </c>
+      <c r="F134" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -3268,6 +3672,9 @@
       <c r="E135" t="n">
         <v>2617.7345</v>
       </c>
+      <c r="F135" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -3289,6 +3696,9 @@
       <c r="E136" t="n">
         <v>2232.4536</v>
       </c>
+      <c r="F136" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -3310,6 +3720,9 @@
       <c r="E137" t="n">
         <v>2564.8028</v>
       </c>
+      <c r="F137" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -3331,6 +3744,9 @@
       <c r="E138" t="n">
         <v>2927.4448</v>
       </c>
+      <c r="F138" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -3352,6 +3768,9 @@
       <c r="E139" t="n">
         <v>4094.25555</v>
       </c>
+      <c r="F139" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -3373,6 +3792,9 @@
       <c r="E140" t="n">
         <v>4678.6222</v>
       </c>
+      <c r="F140" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -3394,6 +3816,9 @@
       <c r="E141" t="n">
         <v>2757.85</v>
       </c>
+      <c r="F141" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -3415,6 +3840,9 @@
       <c r="E142" t="n">
         <v>2061.9035</v>
       </c>
+      <c r="F142" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -3436,6 +3864,9 @@
       <c r="E143" t="n">
         <v>3383.1027</v>
       </c>
+      <c r="F143" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -3457,6 +3888,9 @@
       <c r="E144" t="n">
         <v>1854.45505</v>
       </c>
+      <c r="F144" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -3478,6 +3912,9 @@
       <c r="E145" t="n">
         <v>2576.80445</v>
       </c>
+      <c r="F145" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -3499,6 +3936,9 @@
       <c r="E146" t="n">
         <v>1200.00665</v>
       </c>
+      <c r="F146" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -3520,6 +3960,9 @@
       <c r="E147" t="n">
         <v>1193.48</v>
       </c>
+      <c r="F147" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -3541,6 +3984,9 @@
       <c r="E148" t="n">
         <v>3322.67895</v>
       </c>
+      <c r="F148" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -3562,6 +4008,9 @@
       <c r="E149" t="n">
         <v>3260.82315</v>
       </c>
+      <c r="F149" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -3583,6 +4032,9 @@
       <c r="E150" t="n">
         <v>3320.5408</v>
       </c>
+      <c r="F150" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -3604,6 +4056,9 @@
       <c r="E151" t="n">
         <v>3180.4816</v>
       </c>
+      <c r="F151" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -3625,6 +4080,9 @@
       <c r="E152" t="n">
         <v>2336.3339</v>
       </c>
+      <c r="F152" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -3646,6 +4104,9 @@
       <c r="E153" t="n">
         <v>3309.2032</v>
       </c>
+      <c r="F153" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -3667,6 +4128,9 @@
       <c r="E154" t="n">
         <v>2564.2272</v>
       </c>
+      <c r="F154" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -3688,6 +4152,9 @@
       <c r="E155" t="n">
         <v>2933.5869</v>
       </c>
+      <c r="F155" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -3709,6 +4176,9 @@
       <c r="E156" t="n">
         <v>3793.65625</v>
       </c>
+      <c r="F156" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -3730,6 +4200,9 @@
       <c r="E157" t="n">
         <v>3093.56485</v>
       </c>
+      <c r="F157" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -3751,6 +4224,9 @@
       <c r="E158" t="n">
         <v>2221.83</v>
       </c>
+      <c r="F158" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -3772,6 +4248,9 @@
       <c r="E159" t="n">
         <v>2496.69</v>
       </c>
+      <c r="F159" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -3793,6 +4272,9 @@
       <c r="E160" t="n">
         <v>2135.8183</v>
       </c>
+      <c r="F160" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -3814,6 +4296,9 @@
       <c r="E161" t="n">
         <v>2504.9781</v>
       </c>
+      <c r="F161" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -3835,6 +4320,9 @@
       <c r="E162" t="n">
         <v>2994.65625</v>
       </c>
+      <c r="F162" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -3856,6 +4344,9 @@
       <c r="E163" t="n">
         <v>2416.9969</v>
       </c>
+      <c r="F163" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -3877,6 +4368,9 @@
       <c r="E164" t="n">
         <v>1214.5333</v>
       </c>
+      <c r="F164" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -3898,6 +4392,9 @@
       <c r="E165" t="n">
         <v>3417.3439</v>
       </c>
+      <c r="F165" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -3919,6 +4416,9 @@
       <c r="E166" t="n">
         <v>3477.4982</v>
       </c>
+      <c r="F166" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -3940,6 +4440,9 @@
       <c r="E167" t="n">
         <v>3199.9229</v>
       </c>
+      <c r="F167" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -3961,6 +4464,9 @@
       <c r="E168" t="n">
         <v>2791.4349</v>
       </c>
+      <c r="F168" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -3982,6 +4488,9 @@
       <c r="E169" t="n">
         <v>3285.9716</v>
       </c>
+      <c r="F169" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -4003,6 +4512,9 @@
       <c r="E170" t="n">
         <v>2473.2184</v>
       </c>
+      <c r="F170" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -4024,6 +4536,9 @@
       <c r="E171" t="n">
         <v>2895.0614</v>
       </c>
+      <c r="F171" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -4045,6 +4560,9 @@
       <c r="E172" t="n">
         <v>2366.4072</v>
       </c>
+      <c r="F172" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -4066,6 +4584,9 @@
       <c r="E173" t="n">
         <v>1153.47</v>
       </c>
+      <c r="F173" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -4087,6 +4608,9 @@
       <c r="E174" t="n">
         <v>593.87</v>
       </c>
+      <c r="F174" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -4108,6 +4632,9 @@
       <c r="E175" t="n">
         <v>1172.66</v>
       </c>
+      <c r="F175" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -4129,6 +4656,9 @@
       <c r="E176" t="n">
         <v>2677.72215</v>
       </c>
+      <c r="F176" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -4150,6 +4680,9 @@
       <c r="E177" t="n">
         <v>1364.82</v>
       </c>
+      <c r="F177" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -4171,6 +4704,9 @@
       <c r="E178" t="n">
         <v>1965.6384</v>
       </c>
+      <c r="F178" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -4192,6 +4728,9 @@
       <c r="E179" t="n">
         <v>2020.7372</v>
       </c>
+      <c r="F179" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -4213,6 +4752,9 @@
       <c r="E180" t="n">
         <v>3182.4295</v>
       </c>
+      <c r="F180" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -4234,6 +4776,9 @@
       <c r="E181" t="n">
         <v>3559.9299</v>
       </c>
+      <c r="F181" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -4255,6 +4800,9 @@
       <c r="E182" t="n">
         <v>2858.021</v>
       </c>
+      <c r="F182" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -4276,6 +4824,9 @@
       <c r="E183" t="n">
         <v>1606.761</v>
       </c>
+      <c r="F183" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -4297,6 +4848,9 @@
       <c r="E184" t="n">
         <v>1886.4819</v>
       </c>
+      <c r="F184" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -4318,6 +4872,9 @@
       <c r="E185" t="n">
         <v>3151.7326</v>
       </c>
+      <c r="F185" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -4339,6 +4896,9 @@
       <c r="E186" t="n">
         <v>2280.59935</v>
       </c>
+      <c r="F186" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -4360,6 +4920,9 @@
       <c r="E187" t="n">
         <v>3097.51305</v>
       </c>
+      <c r="F187" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -4381,6 +4944,9 @@
       <c r="E188" t="n">
         <v>2983.8063</v>
       </c>
+      <c r="F188" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -4402,6 +4968,9 @@
       <c r="E189" t="n">
         <v>2789.9163</v>
       </c>
+      <c r="F189" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -4423,6 +4992,9 @@
       <c r="E190" t="n">
         <v>4900.73815</v>
       </c>
+      <c r="F190" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -4444,6 +5016,9 @@
       <c r="E191" t="n">
         <v>3596.76925</v>
       </c>
+      <c r="F191" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -4465,6 +5040,9 @@
       <c r="E192" t="n">
         <v>2285.59175</v>
       </c>
+      <c r="F192" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -4486,6 +5064,9 @@
       <c r="E193" t="n">
         <v>2818.8646</v>
       </c>
+      <c r="F193" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -4507,6 +5088,9 @@
       <c r="E194" t="n">
         <v>3133.9083</v>
       </c>
+      <c r="F194" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -4528,6 +5112,9 @@
       <c r="E195" t="n">
         <v>2515.343</v>
       </c>
+      <c r="F195" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -4549,6 +5136,9 @@
       <c r="E196" t="n">
         <v>1778.7293</v>
       </c>
+      <c r="F196" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -4570,6 +5160,9 @@
       <c r="E197" t="n">
         <v>1849.6882</v>
       </c>
+      <c r="F197" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -4591,6 +5184,9 @@
       <c r="E198" t="n">
         <v>1742.1216</v>
       </c>
+      <c r="F198" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -4612,6 +5208,9 @@
       <c r="E199" t="n">
         <v>1721.3991</v>
       </c>
+      <c r="F199" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -4633,6 +5232,9 @@
       <c r="E200" t="n">
         <v>2914.1772</v>
       </c>
+      <c r="F200" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -4654,6 +5256,9 @@
       <c r="E201" t="n">
         <v>2777.7929</v>
       </c>
+      <c r="F201" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -4675,6 +5280,9 @@
       <c r="E202" t="n">
         <v>3726.90445</v>
       </c>
+      <c r="F202" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -4696,6 +5304,9 @@
       <c r="E203" t="n">
         <v>2433.8312</v>
       </c>
+      <c r="F203" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -4717,6 +5328,9 @@
       <c r="E204" t="n">
         <v>2687.23845</v>
       </c>
+      <c r="F204" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -4738,6 +5352,9 @@
       <c r="E205" t="n">
         <v>2893.7793</v>
       </c>
+      <c r="F205" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -4759,6 +5376,9 @@
       <c r="E206" t="n">
         <v>3143.9367</v>
       </c>
+      <c r="F206" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -4780,6 +5400,9 @@
       <c r="E207" t="n">
         <v>2138.6853</v>
       </c>
+      <c r="F207" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -4801,6 +5424,9 @@
       <c r="E208" t="n">
         <v>3068.0466</v>
       </c>
+      <c r="F208" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -4822,6 +5448,9 @@
       <c r="E209" t="n">
         <v>2385.3264</v>
       </c>
+      <c r="F209" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -4843,6 +5472,9 @@
       <c r="E210" t="n">
         <v>3463.74805</v>
       </c>
+      <c r="F210" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -4864,6 +5496,9 @@
       <c r="E211" t="n">
         <v>3141.471</v>
       </c>
+      <c r="F211" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -4885,6 +5520,9 @@
       <c r="E212" t="n">
         <v>3115.8269</v>
       </c>
+      <c r="F212" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -4906,6 +5544,9 @@
       <c r="E213" t="n">
         <v>2353.2691</v>
       </c>
+      <c r="F213" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -4927,6 +5568,9 @@
       <c r="E214" t="n">
         <v>2197.3909</v>
       </c>
+      <c r="F214" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -4948,6 +5592,9 @@
       <c r="E215" t="n">
         <v>1905.2063</v>
       </c>
+      <c r="F215" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -4969,6 +5616,9 @@
       <c r="E216" t="n">
         <v>1439.787</v>
       </c>
+      <c r="F216" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -4990,6 +5640,9 @@
       <c r="E217" t="n">
         <v>1818.5388</v>
       </c>
+      <c r="F217" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -5011,6 +5664,9 @@
       <c r="E218" t="n">
         <v>4004.9637</v>
       </c>
+      <c r="F218" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -5032,6 +5688,9 @@
       <c r="E219" t="n">
         <v>1287.4505</v>
       </c>
+      <c r="F219" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -5053,6 +5712,9 @@
       <c r="E220" t="n">
         <v>2454.4572</v>
       </c>
+      <c r="F220" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -5074,6 +5736,9 @@
       <c r="E221" t="n">
         <v>3700.2674</v>
       </c>
+      <c r="F221" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -5095,6 +5760,9 @@
       <c r="E222" t="n">
         <v>2774.265</v>
       </c>
+      <c r="F222" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -5116,6 +5784,9 @@
       <c r="E223" t="n">
         <v>3570.7855</v>
       </c>
+      <c r="F223" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -5137,6 +5808,9 @@
       <c r="E224" t="n">
         <v>2253.8194</v>
       </c>
+      <c r="F224" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -5158,6 +5832,9 @@
       <c r="E225" t="n">
         <v>2190.0249</v>
       </c>
+      <c r="F225" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -5179,6 +5856,9 @@
       <c r="E226" t="n">
         <v>2165.8947</v>
       </c>
+      <c r="F226" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -5200,6 +5880,9 @@
       <c r="E227" t="n">
         <v>2988.0337</v>
       </c>
+      <c r="F227" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -5221,6 +5904,9 @@
       <c r="E228" t="n">
         <v>3076.9584</v>
       </c>
+      <c r="F228" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -5242,6 +5928,9 @@
       <c r="E229" t="n">
         <v>2893.0695</v>
       </c>
+      <c r="F229" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -5263,6 +5952,9 @@
       <c r="E230" t="n">
         <v>2846.43</v>
       </c>
+      <c r="F230" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -5284,6 +5976,9 @@
       <c r="E231" t="n">
         <v>2237.7618</v>
       </c>
+      <c r="F231" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -5305,6 +6000,9 @@
       <c r="E232" t="n">
         <v>3932.5725</v>
       </c>
+      <c r="F232" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -5326,6 +6024,9 @@
       <c r="E233" t="n">
         <v>2328.3852</v>
       </c>
+      <c r="F233" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -5347,6 +6048,9 @@
       <c r="E234" t="n">
         <v>2571.836</v>
       </c>
+      <c r="F234" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -5368,6 +6072,9 @@
       <c r="E235" t="n">
         <v>2444.3329</v>
       </c>
+      <c r="F235" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -5389,6 +6096,9 @@
       <c r="E236" t="n">
         <v>2721.5832</v>
       </c>
+      <c r="F236" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -5410,6 +6120,9 @@
       <c r="E237" t="n">
         <v>3268.4999</v>
       </c>
+      <c r="F237" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -5431,6 +6144,9 @@
       <c r="E238" t="n">
         <v>3674.8445</v>
       </c>
+      <c r="F238" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -5452,6 +6168,9 @@
       <c r="E239" t="n">
         <v>3979.6089</v>
       </c>
+      <c r="F239" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -5473,6 +6192,9 @@
       <c r="E240" t="n">
         <v>3407.6971</v>
       </c>
+      <c r="F240" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -5494,6 +6216,9 @@
       <c r="E241" t="n">
         <v>3454.1679</v>
       </c>
+      <c r="F241" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -5515,6 +6240,9 @@
       <c r="E242" t="n">
         <v>3102.7367</v>
       </c>
+      <c r="F242" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -5536,6 +6264,9 @@
       <c r="E243" t="n">
         <v>2869.7483</v>
       </c>
+      <c r="F243" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -5557,6 +6288,9 @@
       <c r="E244" t="n">
         <v>2600.7848</v>
       </c>
+      <c r="F244" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -5578,6 +6312,9 @@
       <c r="E245" t="n">
         <v>2677.0261</v>
       </c>
+      <c r="F245" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -5599,6 +6336,9 @@
       <c r="E246" t="n">
         <v>244.0833</v>
       </c>
+      <c r="F246" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -5620,6 +6360,9 @@
       <c r="E247" t="n">
         <v>1713.4413</v>
       </c>
+      <c r="F247" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -5641,6 +6384,9 @@
       <c r="E248" t="n">
         <v>2325.937</v>
       </c>
+      <c r="F248" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -5662,6 +6408,9 @@
       <c r="E249" t="n">
         <v>2308.9809</v>
       </c>
+      <c r="F249" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -5683,6 +6432,9 @@
       <c r="E250" t="n">
         <v>3584.6071</v>
       </c>
+      <c r="F250" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -5704,6 +6456,9 @@
       <c r="E251" t="n">
         <v>3447.594</v>
       </c>
+      <c r="F251" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -5725,6 +6480,9 @@
       <c r="E252" t="n">
         <v>2478.1368</v>
       </c>
+      <c r="F252" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -5746,6 +6504,9 @@
       <c r="E253" t="n">
         <v>3722.6849</v>
       </c>
+      <c r="F253" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -5767,6 +6528,9 @@
       <c r="E254" t="n">
         <v>3005.1213</v>
       </c>
+      <c r="F254" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -5788,6 +6552,9 @@
       <c r="E255" t="n">
         <v>3059.3988</v>
       </c>
+      <c r="F255" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -5809,6 +6576,9 @@
       <c r="E256" t="n">
         <v>3767.6036</v>
       </c>
+      <c r="F256" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -5830,6 +6600,9 @@
       <c r="E257" t="n">
         <v>1949.8043</v>
       </c>
+      <c r="F257" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -5851,6 +6624,9 @@
       <c r="E258" t="n">
         <v>2136.0162</v>
       </c>
+      <c r="F258" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -5872,6 +6648,9 @@
       <c r="E259" t="n">
         <v>2545.1958</v>
       </c>
+      <c r="F259" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -5893,6 +6672,9 @@
       <c r="E260" t="n">
         <v>3065.7545</v>
       </c>
+      <c r="F260" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -5914,6 +6696,9 @@
       <c r="E261" t="n">
         <v>3077.5475</v>
       </c>
+      <c r="F261" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -5935,6 +6720,9 @@
       <c r="E262" t="n">
         <v>3290.7545</v>
       </c>
+      <c r="F262" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -5956,6 +6744,9 @@
       <c r="E263" t="n">
         <v>3613.5447</v>
       </c>
+      <c r="F263" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -5977,6 +6768,9 @@
       <c r="E264" t="n">
         <v>3715.3571</v>
       </c>
+      <c r="F264" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -5998,6 +6792,9 @@
       <c r="E265" t="n">
         <v>3730.6756</v>
       </c>
+      <c r="F265" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -6019,6 +6816,9 @@
       <c r="E266" t="n">
         <v>2968.191</v>
       </c>
+      <c r="F266" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -6040,6 +6840,9 @@
       <c r="E267" t="n">
         <v>2952.875</v>
       </c>
+      <c r="F267" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -6061,6 +6864,9 @@
       <c r="E268" t="n">
         <v>2989.2676</v>
       </c>
+      <c r="F268" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -6082,6 +6888,9 @@
       <c r="E269" t="n">
         <v>2643.181</v>
       </c>
+      <c r="F269" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -6103,6 +6912,9 @@
       <c r="E270" t="n">
         <v>3150.6118</v>
       </c>
+      <c r="F270" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -6124,6 +6936,9 @@
       <c r="E271" t="n">
         <v>4531.9618</v>
       </c>
+      <c r="F271" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -6145,6 +6960,9 @@
       <c r="E272" t="n">
         <v>4426.4374</v>
       </c>
+      <c r="F272" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -6166,6 +6984,9 @@
       <c r="E273" t="n">
         <v>2426.9992</v>
       </c>
+      <c r="F273" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -6187,6 +7008,9 @@
       <c r="E274" t="n">
         <v>2565.7868</v>
       </c>
+      <c r="F274" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -6208,6 +7032,9 @@
       <c r="E275" t="n">
         <v>3163.5368</v>
       </c>
+      <c r="F275" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -6229,6 +7056,9 @@
       <c r="E276" t="n">
         <v>3301.6314</v>
       </c>
+      <c r="F276" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -6250,6 +7080,9 @@
       <c r="E277" t="n">
         <v>3206.6269</v>
       </c>
+      <c r="F277" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -6271,6 +7104,9 @@
       <c r="E278" t="n">
         <v>3044.4664</v>
       </c>
+      <c r="F278" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -6292,6 +7128,9 @@
       <c r="E279" t="n">
         <v>3012.8642</v>
       </c>
+      <c r="F279" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -6313,6 +7152,9 @@
       <c r="E280" t="n">
         <v>2905.8017</v>
       </c>
+      <c r="F280" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -6334,6 +7176,9 @@
       <c r="E281" t="n">
         <v>3216.0347</v>
       </c>
+      <c r="F281" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -6355,6 +7200,9 @@
       <c r="E282" t="n">
         <v>1753.5979</v>
       </c>
+      <c r="F282" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -6376,6 +7224,9 @@
       <c r="E283" t="n">
         <v>1880.4824</v>
       </c>
+      <c r="F283" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -6397,6 +7248,9 @@
       <c r="E284" t="n">
         <v>1937.4951</v>
       </c>
+      <c r="F284" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -6418,6 +7272,9 @@
       <c r="E285" t="n">
         <v>2499.9146</v>
       </c>
+      <c r="F285" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -6439,6 +7296,9 @@
       <c r="E286" t="n">
         <v>1866.0509</v>
       </c>
+      <c r="F286" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -6460,6 +7320,9 @@
       <c r="E287" t="n">
         <v>2569.292</v>
       </c>
+      <c r="F287" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -6481,6 +7344,9 @@
       <c r="E288" t="n">
         <v>2701.2646</v>
       </c>
+      <c r="F288" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -6502,6 +7368,9 @@
       <c r="E289" t="n">
         <v>2901.7062</v>
       </c>
+      <c r="F289" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -6523,6 +7392,9 @@
       <c r="E290" t="n">
         <v>2719.2304</v>
       </c>
+      <c r="F290" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -6544,6 +7416,9 @@
       <c r="E291" t="n">
         <v>1722.9594</v>
       </c>
+      <c r="F291" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -6565,6 +7440,9 @@
       <c r="E292" t="n">
         <v>2341.3491</v>
       </c>
+      <c r="F292" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -6586,6 +7464,9 @@
       <c r="E293" t="n">
         <v>2462.8053</v>
       </c>
+      <c r="F293" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -6607,6 +7488,9 @@
       <c r="E294" t="n">
         <v>3102.2146</v>
       </c>
+      <c r="F294" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -6628,6 +7512,9 @@
       <c r="E295" t="n">
         <v>3189.0138</v>
       </c>
+      <c r="F295" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -6649,6 +7536,9 @@
       <c r="E296" t="n">
         <v>3062.14</v>
       </c>
+      <c r="F296" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -6670,6 +7560,9 @@
       <c r="E297" t="n">
         <v>2872.1724</v>
       </c>
+      <c r="F297" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -6691,6 +7584,9 @@
       <c r="E298" t="n">
         <v>2498.5176</v>
       </c>
+      <c r="F298" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -6712,6 +7608,9 @@
       <c r="E299" t="n">
         <v>2326.052</v>
       </c>
+      <c r="F299" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -6733,6 +7632,9 @@
       <c r="E300" t="n">
         <v>2289.9702</v>
       </c>
+      <c r="F300" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -6754,6 +7656,9 @@
       <c r="E301" t="n">
         <v>2291.042</v>
       </c>
+      <c r="F301" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -6775,6 +7680,9 @@
       <c r="E302" t="n">
         <v>1761.7676</v>
       </c>
+      <c r="F302" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -6796,6 +7704,9 @@
       <c r="E303" t="n">
         <v>1721.3991</v>
       </c>
+      <c r="F303" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -6817,6 +7728,9 @@
       <c r="E304" t="n">
         <v>3458.795</v>
       </c>
+      <c r="F304" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -6838,6 +7752,9 @@
       <c r="E305" t="n">
         <v>4228.871999999999</v>
       </c>
+      <c r="F305" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -6859,6 +7776,9 @@
       <c r="E306" t="n">
         <v>3278.0568</v>
       </c>
+      <c r="F306" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -6880,6 +7800,9 @@
       <c r="E307" t="n">
         <v>4991.3568</v>
       </c>
+      <c r="F307" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -6901,6 +7824,9 @@
       <c r="E308" t="n">
         <v>5349.7256</v>
       </c>
+      <c r="F308" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -6922,6 +7848,9 @@
       <c r="E309" t="n">
         <v>3500.7646</v>
       </c>
+      <c r="F309" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -6943,6 +7872,9 @@
       <c r="E310" t="n">
         <v>4159.5948</v>
       </c>
+      <c r="F310" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -6964,6 +7896,9 @@
       <c r="E311" t="n">
         <v>3502.7646</v>
       </c>
+      <c r="F311" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -6985,6 +7920,9 @@
       <c r="E312" t="n">
         <v>4956.3756</v>
       </c>
+      <c r="F312" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -7006,6 +7944,9 @@
       <c r="E313" t="n">
         <v>1870.9862</v>
       </c>
+      <c r="F313" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -7027,6 +7968,9 @@
       <c r="E314" t="n">
         <v>2935.2493</v>
       </c>
+      <c r="F314" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -7048,6 +7992,9 @@
       <c r="E315" t="n">
         <v>3603.3799</v>
       </c>
+      <c r="F315" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -7069,6 +8016,9 @@
       <c r="E316" t="n">
         <v>7232.9994</v>
       </c>
+      <c r="F316" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -7090,6 +8040,9 @@
       <c r="E317" t="n">
         <v>4318.2388</v>
       </c>
+      <c r="F317" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -7111,6 +8064,9 @@
       <c r="E318" t="n">
         <v>3330.0381</v>
       </c>
+      <c r="F318" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -7132,6 +8088,9 @@
       <c r="E319" t="n">
         <v>3156.0484</v>
       </c>
+      <c r="F319" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -7153,6 +8112,9 @@
       <c r="E320" t="n">
         <v>3298.8074</v>
       </c>
+      <c r="F320" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -7174,6 +8136,9 @@
       <c r="E321" t="n">
         <v>3697.3565</v>
       </c>
+      <c r="F321" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -7195,6 +8160,9 @@
       <c r="E322" t="n">
         <v>4446.858200000001</v>
       </c>
+      <c r="F322" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -7216,6 +8184,9 @@
       <c r="E323" t="n">
         <v>3448.6614</v>
       </c>
+      <c r="F323" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -7237,6 +8208,9 @@
       <c r="E324" t="n">
         <v>2188.7166</v>
       </c>
+      <c r="F324" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -7258,6 +8232,9 @@
       <c r="E325" t="n">
         <v>2774.7597</v>
       </c>
+      <c r="F325" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -7279,6 +8256,9 @@
       <c r="E326" t="n">
         <v>2916.3028</v>
       </c>
+      <c r="F326" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -7300,6 +8280,9 @@
       <c r="E327" t="n">
         <v>3010.093</v>
       </c>
+      <c r="F327" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -7321,6 +8304,9 @@
       <c r="E328" t="n">
         <v>1798.3875</v>
       </c>
+      <c r="F328" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -7342,6 +8328,9 @@
       <c r="E329" t="n">
         <v>1791.3991</v>
       </c>
+      <c r="F329" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -7363,6 +8352,9 @@
       <c r="E330" t="n">
         <v>2329.5499</v>
       </c>
+      <c r="F330" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -7384,6 +8376,9 @@
       <c r="E331" t="n">
         <v>2792.744</v>
       </c>
+      <c r="F331" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -7405,6 +8400,9 @@
       <c r="E332" t="n">
         <v>2866.6851</v>
       </c>
+      <c r="F332" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -7426,6 +8424,9 @@
       <c r="E333" t="n">
         <v>2850.851</v>
       </c>
+      <c r="F333" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -7447,6 +8448,9 @@
       <c r="E334" t="n">
         <v>2972.3499</v>
       </c>
+      <c r="F334" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -7468,6 +8472,9 @@
       <c r="E335" t="n">
         <v>3709.0592</v>
       </c>
+      <c r="F335" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -7489,6 +8496,9 @@
       <c r="E336" t="n">
         <v>2549.9711</v>
       </c>
+      <c r="F336" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -7510,6 +8520,9 @@
       <c r="E337" t="n">
         <v>2413.4285</v>
       </c>
+      <c r="F337" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -7531,6 +8544,9 @@
       <c r="E338" t="n">
         <v>1980.7336</v>
       </c>
+      <c r="F338" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -7552,6 +8568,9 @@
       <c r="E339" t="n">
         <v>2868.912</v>
       </c>
+      <c r="F339" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -7573,6 +8592,9 @@
       <c r="E340" t="n">
         <v>3112.4492</v>
       </c>
+      <c r="F340" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -7594,6 +8616,9 @@
       <c r="E341" t="n">
         <v>2830.803</v>
       </c>
+      <c r="F341" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -7615,6 +8640,9 @@
       <c r="E342" t="n">
         <v>2288.7852</v>
       </c>
+      <c r="F342" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -7636,6 +8664,9 @@
       <c r="E343" t="n">
         <v>2684.4822</v>
       </c>
+      <c r="F343" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -7657,6 +8688,9 @@
       <c r="E344" t="n">
         <v>2642.4592</v>
       </c>
+      <c r="F344" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -7678,6 +8712,9 @@
       <c r="E345" t="n">
         <v>1857.062</v>
       </c>
+      <c r="F345" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -7699,6 +8736,9 @@
       <c r="E346" t="n">
         <v>2995.6666</v>
       </c>
+      <c r="F346" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -7720,6 +8760,9 @@
       <c r="E347" t="n">
         <v>2039.7156</v>
       </c>
+      <c r="F347" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -7741,6 +8784,9 @@
       <c r="E348" t="n">
         <v>2594.7231</v>
       </c>
+      <c r="F348" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -7762,6 +8808,9 @@
       <c r="E349" t="n">
         <v>3851.9233</v>
       </c>
+      <c r="F349" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -7783,6 +8832,9 @@
       <c r="E350" t="n">
         <v>2686.5854</v>
       </c>
+      <c r="F350" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -7804,6 +8856,9 @@
       <c r="E351" t="n">
         <v>2533.2323</v>
       </c>
+      <c r="F351" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -7825,6 +8880,9 @@
       <c r="E352" t="n">
         <v>2524.8041</v>
       </c>
+      <c r="F352" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -7846,6 +8904,9 @@
       <c r="E353" t="n">
         <v>2247.7705</v>
       </c>
+      <c r="F353" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -7867,6 +8928,9 @@
       <c r="E354" t="n">
         <v>2738.0663</v>
       </c>
+      <c r="F354" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -7888,6 +8952,9 @@
       <c r="E355" t="n">
         <v>3638.4471</v>
       </c>
+      <c r="F355" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -7909,6 +8976,9 @@
       <c r="E356" t="n">
         <v>3560.2053</v>
       </c>
+      <c r="F356" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -7930,6 +9000,9 @@
       <c r="E357" t="n">
         <v>3611.2697</v>
       </c>
+      <c r="F357" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -7951,6 +9024,9 @@
       <c r="E358" t="n">
         <v>3516.0067</v>
       </c>
+      <c r="F358" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -7972,6 +9048,9 @@
       <c r="E359" t="n">
         <v>3086.2165</v>
       </c>
+      <c r="F359" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -7993,6 +9072,9 @@
       <c r="E360" t="n">
         <v>3462.7504</v>
       </c>
+      <c r="F360" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -8014,6 +9096,9 @@
       <c r="E361" t="n">
         <v>4051.3495</v>
       </c>
+      <c r="F361" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -8035,6 +9120,9 @@
       <c r="E362" t="n">
         <v>2599.9109</v>
       </c>
+      <c r="F362" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -8056,6 +9144,9 @@
       <c r="E363" t="n">
         <v>2533.03</v>
       </c>
+      <c r="F363" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -8077,6 +9168,9 @@
       <c r="E364" t="n">
         <v>3823.5031</v>
       </c>
+      <c r="F364" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -8098,6 +9192,9 @@
       <c r="E365" t="n">
         <v>2522.5021</v>
       </c>
+      <c r="F365" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -8119,6 +9216,9 @@
       <c r="E366" t="n">
         <v>2676.395</v>
       </c>
+      <c r="F366" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -8140,6 +9240,9 @@
       <c r="E367" t="n">
         <v>1992.1531</v>
       </c>
+      <c r="F367" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -8161,6 +9264,9 @@
       <c r="E368" t="n">
         <v>3193.4956</v>
       </c>
+      <c r="F368" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -8182,6 +9288,9 @@
       <c r="E369" t="n">
         <v>2375.7778</v>
       </c>
+      <c r="F369" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -8203,6 +9312,9 @@
       <c r="E370" t="n">
         <v>3120.29</v>
       </c>
+      <c r="F370" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -8224,6 +9336,9 @@
       <c r="E371" t="n">
         <v>3260.8223</v>
       </c>
+      <c r="F371" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -8245,6 +9360,9 @@
       <c r="E372" t="n">
         <v>4510.8223</v>
       </c>
+      <c r="F372" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -8266,6 +9384,9 @@
       <c r="E373" t="n">
         <v>4567.7068</v>
       </c>
+      <c r="F373" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -8287,6 +9408,9 @@
       <c r="E374" t="n">
         <v>3697.2091</v>
       </c>
+      <c r="F374" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -8308,6 +9432,9 @@
       <c r="E375" t="n">
         <v>3144.3699</v>
       </c>
+      <c r="F375" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -8329,6 +9456,9 @@
       <c r="E376" t="n">
         <v>4342.3278</v>
       </c>
+      <c r="F376" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -8350,6 +9480,9 @@
       <c r="E377" t="n">
         <v>4380.5712</v>
       </c>
+      <c r="F377" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -8371,6 +9504,9 @@
       <c r="E378" t="n">
         <v>4245.0599</v>
       </c>
+      <c r="F378" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -8392,6 +9528,9 @@
       <c r="E379" t="n">
         <v>2718.3778</v>
       </c>
+      <c r="F379" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -8413,6 +9552,9 @@
       <c r="E380" t="n">
         <v>3598.5031</v>
       </c>
+      <c r="F380" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -8434,6 +9576,9 @@
       <c r="E381" t="n">
         <v>3816.4563</v>
       </c>
+      <c r="F381" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -8455,6 +9600,9 @@
       <c r="E382" t="n">
         <v>1992.6049</v>
       </c>
+      <c r="F382" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -8476,6 +9624,9 @@
       <c r="E383" t="n">
         <v>2847.2324</v>
       </c>
+      <c r="F383" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -8497,6 +9648,9 @@
       <c r="E384" t="n">
         <v>3692.5297</v>
       </c>
+      <c r="F384" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -8518,6 +9672,9 @@
       <c r="E385" t="n">
         <v>2743.7123</v>
       </c>
+      <c r="F385" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -8539,6 +9696,9 @@
       <c r="E386" t="n">
         <v>2854.4462</v>
       </c>
+      <c r="F386" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -8560,6 +9720,9 @@
       <c r="E387" t="n">
         <v>2793.9071</v>
       </c>
+      <c r="F387" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -8581,6 +9744,9 @@
       <c r="E388" t="n">
         <v>2837.4887</v>
       </c>
+      <c r="F388" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -8602,6 +9768,9 @@
       <c r="E389" t="n">
         <v>2515.9446</v>
       </c>
+      <c r="F389" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -8623,6 +9792,9 @@
       <c r="E390" t="n">
         <v>3248.5349</v>
       </c>
+      <c r="F390" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -8644,6 +9816,9 @@
       <c r="E391" t="n">
         <v>3025.4907</v>
       </c>
+      <c r="F391" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -8665,6 +9840,9 @@
       <c r="E392" t="n">
         <v>1925.1714</v>
       </c>
+      <c r="F392" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -8686,6 +9864,9 @@
       <c r="E393" t="n">
         <v>3685.406</v>
       </c>
+      <c r="F393" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -8707,6 +9888,9 @@
       <c r="E394" t="n">
         <v>3753.6018</v>
       </c>
+      <c r="F394" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -8728,6 +9912,9 @@
       <c r="E395" t="n">
         <v>2986.5271</v>
       </c>
+      <c r="F395" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -8749,6 +9936,9 @@
       <c r="E396" t="n">
         <v>3124.0014</v>
       </c>
+      <c r="F396" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -8770,6 +9960,9 @@
       <c r="E397" t="n">
         <v>2980.7792</v>
       </c>
+      <c r="F397" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -8791,6 +9984,9 @@
       <c r="E398" t="n">
         <v>3137.1413</v>
       </c>
+      <c r="F398" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -8812,6 +10008,9 @@
       <c r="E399" t="n">
         <v>4029.5505</v>
       </c>
+      <c r="F399" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -8833,6 +10032,9 @@
       <c r="E400" t="n">
         <v>4348.001899999999</v>
       </c>
+      <c r="F400" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -8854,6 +10056,9 @@
       <c r="E401" t="n">
         <v>3415.406</v>
       </c>
+      <c r="F401" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -8875,6 +10080,9 @@
       <c r="E402" t="n">
         <v>2443.8346</v>
       </c>
+      <c r="F402" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -8896,6 +10104,9 @@
       <c r="E403" t="n">
         <v>2761.0542</v>
       </c>
+      <c r="F403" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -8917,6 +10128,9 @@
       <c r="E404" t="n">
         <v>2699.3572</v>
       </c>
+      <c r="F404" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -8938,6 +10152,9 @@
       <c r="E405" t="n">
         <v>2700.4</v>
       </c>
+      <c r="F405" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -8959,6 +10176,9 @@
       <c r="E406" t="n">
         <v>2639.9311</v>
       </c>
+      <c r="F406" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -8980,6 +10200,9 @@
       <c r="E407" t="n">
         <v>2027.5778</v>
       </c>
+      <c r="F407" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -9001,6 +10224,9 @@
       <c r="E408" t="n">
         <v>2988.7336</v>
       </c>
+      <c r="F408" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -9022,6 +10248,9 @@
       <c r="E409" t="n">
         <v>3171.4475</v>
       </c>
+      <c r="F409" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -9043,6 +10272,9 @@
       <c r="E410" t="n">
         <v>1825.604</v>
       </c>
+      <c r="F410" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -9064,6 +10296,9 @@
       <c r="E411" t="n">
         <v>3141.0453</v>
       </c>
+      <c r="F411" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -9085,6 +10320,9 @@
       <c r="E412" t="n">
         <v>3864.0198</v>
       </c>
+      <c r="F412" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -9106,6 +10344,9 @@
       <c r="E413" t="n">
         <v>3009.946</v>
       </c>
+      <c r="F413" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -9127,6 +10368,9 @@
       <c r="E414" t="n">
         <v>1992.5193</v>
       </c>
+      <c r="F414" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -9148,6 +10392,9 @@
       <c r="E415" t="n">
         <v>2375.1144</v>
       </c>
+      <c r="F415" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -9169,6 +10416,9 @@
       <c r="E416" t="n">
         <v>3601.856</v>
       </c>
+      <c r="F416" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -9190,6 +10440,9 @@
       <c r="E417" t="n">
         <v>1779.2132</v>
       </c>
+      <c r="F417" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -9211,6 +10464,9 @@
       <c r="E418" t="n">
         <v>3123.5039</v>
       </c>
+      <c r="F418" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -9232,6 +10488,9 @@
       <c r="E419" t="n">
         <v>2978.9114</v>
       </c>
+      <c r="F419" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -9253,6 +10512,9 @@
       <c r="E420" t="n">
         <v>3028.5405</v>
       </c>
+      <c r="F420" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -9274,6 +10536,9 @@
       <c r="E421" t="n">
         <v>3029.5405</v>
       </c>
+      <c r="F421" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -9295,6 +10560,9 @@
       <c r="E422" t="n">
         <v>2928.0287</v>
       </c>
+      <c r="F422" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -9316,6 +10584,9 @@
       <c r="E423" t="n">
         <v>2797.4426</v>
       </c>
+      <c r="F423" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -9337,6 +10608,9 @@
       <c r="E424" t="n">
         <v>3113.1883</v>
       </c>
+      <c r="F424" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -9358,6 +10632,9 @@
       <c r="E425" t="n">
         <v>3585.8228</v>
       </c>
+      <c r="F425" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -9379,6 +10656,9 @@
       <c r="E426" t="n">
         <v>2997.176</v>
       </c>
+      <c r="F426" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -9400,6 +10680,9 @@
       <c r="E427" t="n">
         <v>5779.3616</v>
       </c>
+      <c r="F427" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -9421,6 +10704,9 @@
       <c r="E428" t="n">
         <v>5178.366</v>
       </c>
+      <c r="F428" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -9442,6 +10728,9 @@
       <c r="E429" t="n">
         <v>5224.6608</v>
       </c>
+      <c r="F429" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -9463,6 +10752,9 @@
       <c r="E430" t="n">
         <v>5134.6605</v>
       </c>
+      <c r="F430" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -9484,6 +10776,9 @@
       <c r="E431" t="n">
         <v>4496.9952</v>
       </c>
+      <c r="F431" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -9505,6 +10800,9 @@
       <c r="E432" t="n">
         <v>2715.7593</v>
       </c>
+      <c r="F432" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -9526,6 +10824,9 @@
       <c r="E433" t="n">
         <v>3979.5105</v>
       </c>
+      <c r="F433" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -9547,6 +10848,9 @@
       <c r="E434" t="n">
         <v>3937.9931</v>
       </c>
+      <c r="F434" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -9568,6 +10872,9 @@
       <c r="E435" t="n">
         <v>4014.4593</v>
       </c>
+      <c r="F435" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -9589,6 +10896,9 @@
       <c r="E436" t="n">
         <v>4310.123900000001</v>
       </c>
+      <c r="F436" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -9610,6 +10920,9 @@
       <c r="E437" t="n">
         <v>4512.6105</v>
       </c>
+      <c r="F437" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -9631,6 +10944,9 @@
       <c r="E438" t="n">
         <v>6579.0568</v>
       </c>
+      <c r="F438" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -9652,6 +10968,9 @@
       <c r="E439" t="n">
         <v>2049.216</v>
       </c>
+      <c r="F439" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -9673,6 +10992,9 @@
       <c r="E440" t="n">
         <v>4222.4472</v>
       </c>
+      <c r="F440" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -9694,6 +11016,9 @@
       <c r="E441" t="n">
         <v>1349.368</v>
       </c>
+      <c r="F441" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -9715,6 +11040,9 @@
       <c r="E442" t="n">
         <v>4338.996999999999</v>
       </c>
+      <c r="F442" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -9736,6 +11064,9 @@
       <c r="E443" t="n">
         <v>3785.7716</v>
       </c>
+      <c r="F443" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -9757,6 +11088,9 @@
       <c r="E444" t="n">
         <v>2507.5963</v>
       </c>
+      <c r="F444" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -9778,6 +11112,9 @@
       <c r="E445" t="n">
         <v>3488.2095</v>
       </c>
+      <c r="F445" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -9799,6 +11136,9 @@
       <c r="E446" t="n">
         <v>2237.0595</v>
       </c>
+      <c r="F446" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -9820,6 +11160,9 @@
       <c r="E447" t="n">
         <v>2999.5416</v>
       </c>
+      <c r="F447" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -9841,6 +11184,9 @@
       <c r="E448" t="n">
         <v>1720.2707</v>
       </c>
+      <c r="F448" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -9862,6 +11208,9 @@
       <c r="E449" t="n">
         <v>2071.7991</v>
       </c>
+      <c r="F449" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -9883,6 +11232,9 @@
       <c r="E450" t="n">
         <v>2198.3221</v>
       </c>
+      <c r="F450" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -9904,6 +11256,9 @@
       <c r="E451" t="n">
         <v>2205.8962</v>
       </c>
+      <c r="F451" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -9925,6 +11280,9 @@
       <c r="E452" t="n">
         <v>2049.3221</v>
       </c>
+      <c r="F452" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -9946,6 +11304,9 @@
       <c r="E453" t="n">
         <v>2792.3712</v>
       </c>
+      <c r="F453" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -9967,6 +11328,9 @@
       <c r="E454" t="n">
         <v>2940.7386</v>
       </c>
+      <c r="F454" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -9988,6 +11352,9 @@
       <c r="E455" t="n">
         <v>3160.3646</v>
       </c>
+      <c r="F455" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -10009,6 +11376,9 @@
       <c r="E456" t="n">
         <v>3152.7905</v>
       </c>
+      <c r="F456" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -10030,6 +11400,9 @@
       <c r="E457" t="n">
         <v>3006.6707</v>
       </c>
+      <c r="F457" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -10051,6 +11424,9 @@
       <c r="E458" t="n">
         <v>4358.5558</v>
       </c>
+      <c r="F458" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -10072,6 +11448,9 @@
       <c r="E459" t="n">
         <v>4764.5191</v>
       </c>
+      <c r="F459" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -10093,6 +11472,9 @@
       <c r="E460" t="n">
         <v>2883.7093</v>
       </c>
+      <c r="F460" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -10114,6 +11496,9 @@
       <c r="E461" t="n">
         <v>2255.0412</v>
       </c>
+      <c r="F461" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -10135,6 +11520,9 @@
       <c r="E462" t="n">
         <v>3199.497</v>
       </c>
+      <c r="F462" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -10156,6 +11544,9 @@
       <c r="E463" t="n">
         <v>1971.2373</v>
       </c>
+      <c r="F463" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -10177,6 +11568,9 @@
       <c r="E464" t="n">
         <v>2354.121</v>
       </c>
+      <c r="F464" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -10198,6 +11592,9 @@
       <c r="E465" t="n">
         <v>3149.002</v>
       </c>
+      <c r="F465" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -10219,6 +11616,9 @@
       <c r="E466" t="n">
         <v>3298.5751</v>
       </c>
+      <c r="F466" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -10240,6 +11640,9 @@
       <c r="E467" t="n">
         <v>3260.8051</v>
       </c>
+      <c r="F467" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -10261,6 +11664,9 @@
       <c r="E468" t="n">
         <v>1705.0244</v>
       </c>
+      <c r="F468" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -10282,6 +11688,9 @@
       <c r="E469" t="n">
         <v>2489.7776</v>
       </c>
+      <c r="F469" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -10303,6 +11712,9 @@
       <c r="E470" t="n">
         <v>2467.509</v>
       </c>
+      <c r="F470" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -10324,6 +11736,9 @@
       <c r="E471" t="n">
         <v>1990.4798</v>
       </c>
+      <c r="F471" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -10345,6 +11760,9 @@
       <c r="E472" t="n">
         <v>3226.0499</v>
       </c>
+      <c r="F472" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -10366,6 +11784,9 @@
       <c r="E473" t="n">
         <v>2454.3111</v>
       </c>
+      <c r="F473" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -10387,6 +11808,9 @@
       <c r="E474" t="n">
         <v>1682.4369</v>
       </c>
+      <c r="F474" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -10408,6 +11832,9 @@
       <c r="E475" t="n">
         <v>1605.4845</v>
       </c>
+      <c r="F475" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -10429,6 +11856,9 @@
       <c r="E476" t="n">
         <v>1535.95</v>
       </c>
+      <c r="F476" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -10450,6 +11880,9 @@
       <c r="E477" t="n">
         <v>3019.8521</v>
       </c>
+      <c r="F477" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -10471,6 +11904,9 @@
       <c r="E478" t="n">
         <v>2623.5148</v>
       </c>
+      <c r="F478" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -10492,6 +11928,9 @@
       <c r="E479" t="n">
         <v>2325.2333</v>
       </c>
+      <c r="F479" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -10513,6 +11952,9 @@
       <c r="E480" t="n">
         <v>3536.16</v>
       </c>
+      <c r="F480" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -10534,6 +11976,9 @@
       <c r="E481" t="n">
         <v>2314.4645</v>
       </c>
+      <c r="F481" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -10555,6 +12000,9 @@
       <c r="E482" t="n">
         <v>760</v>
       </c>
+      <c r="F482" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -10576,6 +12024,9 @@
       <c r="E483" t="n">
         <v>3182.6294</v>
       </c>
+      <c r="F483" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -10597,6 +12048,9 @@
       <c r="E484" t="n">
         <v>4445.8183</v>
       </c>
+      <c r="F484" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -10618,6 +12072,9 @@
       <c r="E485" t="n">
         <v>4608.1038</v>
       </c>
+      <c r="F485" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -10639,6 +12096,9 @@
       <c r="E486" t="n">
         <v>3623.820999999999</v>
       </c>
+      <c r="F486" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -10660,6 +12120,9 @@
       <c r="E487" t="n">
         <v>2289.6895</v>
       </c>
+      <c r="F487" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -10681,6 +12144,9 @@
       <c r="E488" t="n">
         <v>3641.6019</v>
       </c>
+      <c r="F488" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -10702,6 +12168,9 @@
       <c r="E489" t="n">
         <v>3742.2712</v>
       </c>
+      <c r="F489" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -10723,6 +12192,9 @@
       <c r="E490" t="n">
         <v>2451.15</v>
       </c>
+      <c r="F490" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -10744,6 +12216,9 @@
       <c r="E491" t="n">
         <v>2974.1845</v>
       </c>
+      <c r="F491" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -10765,6 +12240,9 @@
       <c r="E492" t="n">
         <v>3065.6542</v>
       </c>
+      <c r="F492" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -10786,6 +12264,9 @@
       <c r="E493" t="n">
         <v>2843.9845</v>
       </c>
+      <c r="F493" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -10807,6 +12288,9 @@
       <c r="E494" t="n">
         <v>2787.1</v>
       </c>
+      <c r="F494" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -10828,6 +12312,9 @@
       <c r="E495" t="n">
         <v>2862.1</v>
       </c>
+      <c r="F495" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -10849,6 +12336,9 @@
       <c r="E496" t="n">
         <v>2231.0841</v>
       </c>
+      <c r="F496" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -10870,6 +12360,9 @@
       <c r="E497" t="n">
         <v>2465.0349</v>
       </c>
+      <c r="F497" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -10891,6 +12384,9 @@
       <c r="E498" t="n">
         <v>1967.4018</v>
       </c>
+      <c r="F498" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -10912,6 +12408,9 @@
       <c r="E499" t="n">
         <v>2374.3518</v>
       </c>
+      <c r="F499" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -10933,6 +12432,9 @@
       <c r="E500" t="n">
         <v>3550.5823</v>
       </c>
+      <c r="F500" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -10954,6 +12456,9 @@
       <c r="E501" t="n">
         <v>3549.5823</v>
       </c>
+      <c r="F501" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -10975,6 +12480,9 @@
       <c r="E502" t="n">
         <v>3469.5819</v>
       </c>
+      <c r="F502" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -10996,6 +12504,9 @@
       <c r="E503" t="n">
         <v>4621.5952</v>
       </c>
+      <c r="F503" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -11017,6 +12528,9 @@
       <c r="E504" t="n">
         <v>3415.0644</v>
       </c>
+      <c r="F504" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -11038,6 +12552,9 @@
       <c r="E505" t="n">
         <v>3690.1226</v>
       </c>
+      <c r="F505" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -11059,6 +12576,9 @@
       <c r="E506" t="n">
         <v>2294.0345</v>
       </c>
+      <c r="F506" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -11080,6 +12600,9 @@
       <c r="E507" t="n">
         <v>1124</v>
       </c>
+      <c r="F507" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -11101,6 +12624,9 @@
       <c r="E508" t="n">
         <v>1125</v>
       </c>
+      <c r="F508" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -11122,6 +12648,9 @@
       <c r="E509" t="n">
         <v>1681.4369</v>
       </c>
+      <c r="F509" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -11143,6 +12672,9 @@
       <c r="E510" t="n">
         <v>3128.8321</v>
       </c>
+      <c r="F510" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -11164,6 +12696,9 @@
       <c r="E511" t="n">
         <v>1886.4823</v>
       </c>
+      <c r="F511" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -11185,6 +12720,9 @@
       <c r="E512" t="n">
         <v>3137.6323</v>
       </c>
+      <c r="F512" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -11206,6 +12744,9 @@
       <c r="E513" t="n">
         <v>2111.3799</v>
       </c>
+      <c r="F513" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -11227,6 +12768,9 @@
       <c r="E514" t="n">
         <v>3469.5821</v>
       </c>
+      <c r="F514" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -11248,6 +12792,9 @@
       <c r="E515" t="n">
         <v>2330.87</v>
       </c>
+      <c r="F515" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -11269,6 +12816,9 @@
       <c r="E516" t="n">
         <v>2331.87</v>
       </c>
+      <c r="F516" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
@@ -11290,6 +12840,9 @@
       <c r="E517" t="n">
         <v>1719.06</v>
       </c>
+      <c r="F517" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -11311,6 +12864,9 @@
       <c r="E518" t="n">
         <v>1543.6</v>
       </c>
+      <c r="F518" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
@@ -11332,6 +12888,9 @@
       <c r="E519" t="n">
         <v>1552.5528</v>
       </c>
+      <c r="F519" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -11353,6 +12912,9 @@
       <c r="E520" t="n">
         <v>2087.15</v>
       </c>
+      <c r="F520" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -11374,6 +12936,9 @@
       <c r="E521" t="n">
         <v>2655.35</v>
       </c>
+      <c r="F521" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -11395,6 +12960,9 @@
       <c r="E522" t="n">
         <v>2358.7145</v>
       </c>
+      <c r="F522" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
@@ -11416,6 +12984,9 @@
       <c r="E523" t="n">
         <v>3873.6526</v>
       </c>
+      <c r="F523" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
@@ -11437,6 +13008,9 @@
       <c r="E524" t="n">
         <v>2667.9878</v>
       </c>
+      <c r="F524" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
@@ -11458,6 +13032,9 @@
       <c r="E525" t="n">
         <v>2731.7402</v>
       </c>
+      <c r="F525" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -11479,6 +13056,9 @@
       <c r="E526" t="n">
         <v>3214.6277</v>
       </c>
+      <c r="F526" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -11500,6 +13080,9 @@
       <c r="E527" t="n">
         <v>3930.3368</v>
       </c>
+      <c r="F527" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
@@ -11521,6 +13104,9 @@
       <c r="E528" t="n">
         <v>2734.7342</v>
       </c>
+      <c r="F528" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
@@ -11542,6 +13128,9 @@
       <c r="E529" t="n">
         <v>3981.8028</v>
       </c>
+      <c r="F529" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
@@ -11563,6 +13152,9 @@
       <c r="E530" t="n">
         <v>2149.3852</v>
       </c>
+      <c r="F530" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
@@ -11584,6 +13176,9 @@
       <c r="E531" t="n">
         <v>2944.7599</v>
       </c>
+      <c r="F531" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -11605,6 +13200,9 @@
       <c r="E532" t="n">
         <v>4007.79</v>
       </c>
+      <c r="F532" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
@@ -11626,6 +13224,9 @@
       <c r="E533" t="n">
         <v>4156.397</v>
       </c>
+      <c r="F533" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
@@ -11647,6 +13248,9 @@
       <c r="E534" t="n">
         <v>3496.3331</v>
       </c>
+      <c r="F534" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -11668,6 +13272,9 @@
       <c r="E535" t="n">
         <v>2477.8472</v>
       </c>
+      <c r="F535" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
@@ -11689,6 +13296,9 @@
       <c r="E536" t="n">
         <v>918.9528</v>
       </c>
+      <c r="F536" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -11710,6 +13320,9 @@
       <c r="E537" t="n">
         <v>2366.35</v>
       </c>
+      <c r="F537" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -11731,6 +13344,9 @@
       <c r="E538" t="n">
         <v>2484.4638</v>
       </c>
+      <c r="F538" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -11752,6 +13368,9 @@
       <c r="E539" t="n">
         <v>3175.7626</v>
       </c>
+      <c r="F539" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -11773,6 +13392,9 @@
       <c r="E540" t="n">
         <v>3253.0669</v>
       </c>
+      <c r="F540" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -11794,6 +13416,9 @@
       <c r="E541" t="n">
         <v>2425.989</v>
       </c>
+      <c r="F541" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
@@ -11815,6 +13440,9 @@
       <c r="E542" t="n">
         <v>3778.3859</v>
       </c>
+      <c r="F542" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
@@ -11836,6 +13464,9 @@
       <c r="E543" t="n">
         <v>4561.5994</v>
       </c>
+      <c r="F543" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
@@ -11857,6 +13488,9 @@
       <c r="E544" t="n">
         <v>2387.775</v>
       </c>
+      <c r="F544" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
@@ -11878,6 +13512,9 @@
       <c r="E545" t="n">
         <v>2390.5518</v>
       </c>
+      <c r="F545" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
@@ -11899,6 +13536,9 @@
       <c r="E546" t="n">
         <v>3240.1969</v>
       </c>
+      <c r="F546" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
@@ -11920,6 +13560,9 @@
       <c r="E547" t="n">
         <v>3210.3049</v>
       </c>
+      <c r="F547" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
@@ -11941,6 +13584,9 @@
       <c r="E548" t="n">
         <v>2982.1118</v>
       </c>
+      <c r="F548" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
@@ -11962,6 +13608,9 @@
       <c r="E549" t="n">
         <v>2757.0244</v>
       </c>
+      <c r="F549" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
@@ -11983,6 +13632,9 @@
       <c r="E550" t="n">
         <v>2485.1779</v>
       </c>
+      <c r="F550" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
@@ -12004,6 +13656,9 @@
       <c r="E551" t="n">
         <v>3385.5776</v>
       </c>
+      <c r="F551" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
@@ -12025,6 +13680,9 @@
       <c r="E552" t="n">
         <v>4188.5702</v>
       </c>
+      <c r="F552" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
@@ -12046,6 +13704,9 @@
       <c r="E553" t="n">
         <v>3677.4489</v>
       </c>
+      <c r="F553" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
@@ -12067,6 +13728,9 @@
       <c r="E554" t="n">
         <v>2365.437</v>
       </c>
+      <c r="F554" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
@@ -12088,6 +13752,9 @@
       <c r="E555" t="n">
         <v>3747.7145</v>
       </c>
+      <c r="F555" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
@@ -12109,6 +13776,9 @@
       <c r="E556" t="n">
         <v>3081.281</v>
       </c>
+      <c r="F556" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
@@ -12130,6 +13800,9 @@
       <c r="E557" t="n">
         <v>3021.83</v>
       </c>
+      <c r="F557" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
@@ -12151,6 +13824,9 @@
       <c r="E558" t="n">
         <v>3020.83</v>
       </c>
+      <c r="F558" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
@@ -12172,6 +13848,9 @@
       <c r="E559" t="n">
         <v>3850.5444</v>
       </c>
+      <c r="F559" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
@@ -12193,6 +13872,9 @@
       <c r="E560" t="n">
         <v>3868.6526</v>
       </c>
+      <c r="F560" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
@@ -12214,6 +13896,9 @@
       <c r="E561" t="n">
         <v>3813.0267</v>
       </c>
+      <c r="F561" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
@@ -12235,6 +13920,9 @@
       <c r="E562" t="n">
         <v>2325.3297</v>
       </c>
+      <c r="F562" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
@@ -12256,6 +13944,9 @@
       <c r="E563" t="n">
         <v>3098.1596</v>
       </c>
+      <c r="F563" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
@@ -12277,6 +13968,9 @@
       <c r="E564" t="n">
         <v>4504.6226</v>
       </c>
+      <c r="F564" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
@@ -12298,6 +13992,9 @@
       <c r="E565" t="n">
         <v>2222.83</v>
       </c>
+      <c r="F565" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
@@ -12319,6 +14016,9 @@
       <c r="E566" t="n">
         <v>2359.8484</v>
       </c>
+      <c r="F566" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
@@ -12340,6 +14040,9 @@
       <c r="E567" t="n">
         <v>3748.7145</v>
       </c>
+      <c r="F567" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
@@ -12361,6 +14064,9 @@
       <c r="E568" t="n">
         <v>3021.83</v>
       </c>
+      <c r="F568" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
@@ -12382,6 +14088,9 @@
       <c r="E569" t="n">
         <v>3740.4673</v>
       </c>
+      <c r="F569" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
@@ -12403,6 +14112,9 @@
       <c r="E570" t="n">
         <v>3013.6177</v>
       </c>
+      <c r="F570" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
@@ -12424,6 +14136,9 @@
       <c r="E571" t="n">
         <v>1241.5533</v>
       </c>
+      <c r="F571" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
@@ -12445,6 +14160,9 @@
       <c r="E572" t="n">
         <v>3014.6177</v>
       </c>
+      <c r="F572" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
@@ -12466,6 +14184,9 @@
       <c r="E573" t="n">
         <v>2176.0515</v>
       </c>
+      <c r="F573" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
@@ -12487,6 +14208,9 @@
       <c r="E574" t="n">
         <v>2241.6714</v>
       </c>
+      <c r="F574" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
@@ -12508,6 +14232,9 @@
       <c r="E575" t="n">
         <v>2359.87</v>
       </c>
+      <c r="F575" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
@@ -12529,6 +14256,9 @@
       <c r="E576" t="n">
         <v>3742.2217</v>
       </c>
+      <c r="F576" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
@@ -12550,6 +14280,9 @@
       <c r="E577" t="n">
         <v>3129.0801</v>
       </c>
+      <c r="F577" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
@@ -12571,6 +14304,9 @@
       <c r="E578" t="n">
         <v>3811.7928</v>
       </c>
+      <c r="F578" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
@@ -12592,6 +14328,9 @@
       <c r="E579" t="n">
         <v>2112.3</v>
       </c>
+      <c r="F579" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
@@ -12613,6 +14352,9 @@
       <c r="E580" t="n">
         <v>2896.7692</v>
       </c>
+      <c r="F580" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="581">
       <c r="A581" t="inlineStr">
@@ -12634,6 +14376,9 @@
       <c r="E581" t="n">
         <v>1392.3867</v>
       </c>
+      <c r="F581" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="582">
       <c r="A582" t="inlineStr">
@@ -12655,6 +14400,9 @@
       <c r="E582" t="n">
         <v>1309.2435</v>
       </c>
+      <c r="F582" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="583">
       <c r="A583" t="inlineStr">
@@ -12676,6 +14424,9 @@
       <c r="E583" t="n">
         <v>2218.2136</v>
       </c>
+      <c r="F583" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="584">
       <c r="A584" t="inlineStr">
@@ -12697,6 +14448,9 @@
       <c r="E584" t="n">
         <v>3944.8949</v>
       </c>
+      <c r="F584" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="585">
       <c r="A585" t="inlineStr">
@@ -12718,6 +14472,9 @@
       <c r="E585" t="n">
         <v>4171.03</v>
       </c>
+      <c r="F585" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="586">
       <c r="A586" t="inlineStr">
@@ -12739,6 +14496,9 @@
       <c r="E586" t="n">
         <v>2628.2499</v>
       </c>
+      <c r="F586" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="587">
       <c r="A587" t="inlineStr">
@@ -12760,6 +14520,9 @@
       <c r="E587" t="n">
         <v>1991.3045</v>
       </c>
+      <c r="F587" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="588">
       <c r="A588" t="inlineStr">
@@ -12781,6 +14544,9 @@
       <c r="E588" t="n">
         <v>2207.4372</v>
       </c>
+      <c r="F588" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="589">
       <c r="A589" t="inlineStr">
@@ -12802,6 +14568,9 @@
       <c r="E589" t="n">
         <v>1228.5</v>
       </c>
+      <c r="F589" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="590">
       <c r="A590" t="inlineStr">
@@ -12823,6 +14592,9 @@
       <c r="E590" t="n">
         <v>2607.7765</v>
       </c>
+      <c r="F590" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="591">
       <c r="A591" t="inlineStr">
@@ -12844,6 +14616,9 @@
       <c r="E591" t="n">
         <v>2655.2655</v>
       </c>
+      <c r="F591" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="592">
       <c r="A592" t="inlineStr">
@@ -12865,6 +14640,9 @@
       <c r="E592" t="n">
         <v>2689.4174</v>
       </c>
+      <c r="F592" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="593">
       <c r="A593" t="inlineStr">
@@ -12886,6 +14664,9 @@
       <c r="E593" t="n">
         <v>3845.1058</v>
       </c>
+      <c r="F593" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="594">
       <c r="A594" t="inlineStr">
@@ -12907,6 +14688,9 @@
       <c r="E594" t="n">
         <v>4107.5403</v>
       </c>
+      <c r="F594" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="595">
       <c r="A595" t="inlineStr">
@@ -12928,6 +14712,9 @@
       <c r="E595" t="n">
         <v>2720.6633</v>
       </c>
+      <c r="F595" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="596">
       <c r="A596" t="inlineStr">
@@ -12949,6 +14736,9 @@
       <c r="E596" t="n">
         <v>3069.4638</v>
       </c>
+      <c r="F596" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="597">
       <c r="A597" t="inlineStr">
@@ -12970,6 +14760,9 @@
       <c r="E597" t="n">
         <v>2025.9246</v>
       </c>
+      <c r="F597" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="598">
       <c r="A598" t="inlineStr">
@@ -12991,6 +14784,9 @@
       <c r="E598" t="n">
         <v>2141.2225</v>
       </c>
+      <c r="F598" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="599">
       <c r="A599" t="inlineStr">
@@ -13012,6 +14808,9 @@
       <c r="E599" t="n">
         <v>2025.9246</v>
       </c>
+      <c r="F599" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="600">
       <c r="A600" t="inlineStr">
@@ -13033,6 +14832,9 @@
       <c r="E600" t="n">
         <v>2721.4091</v>
       </c>
+      <c r="F600" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
@@ -13054,6 +14856,9 @@
       <c r="E601" t="n">
         <v>3004.1101</v>
       </c>
+      <c r="F601" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="602">
       <c r="A602" t="inlineStr">
@@ -13075,6 +14880,9 @@
       <c r="E602" t="n">
         <v>2552.7692</v>
       </c>
+      <c r="F602" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="603">
       <c r="A603" t="inlineStr">
@@ -13096,6 +14904,9 @@
       <c r="E603" t="n">
         <v>2747.7045</v>
       </c>
+      <c r="F603" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="604">
       <c r="A604" t="inlineStr">
@@ -13117,6 +14928,9 @@
       <c r="E604" t="n">
         <v>2689.82</v>
       </c>
+      <c r="F604" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="605">
       <c r="A605" t="inlineStr">
@@ -13138,6 +14952,9 @@
       <c r="E605" t="n">
         <v>2080.4742</v>
       </c>
+      <c r="F605" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="606">
       <c r="A606" t="inlineStr">
@@ -13159,6 +14976,9 @@
       <c r="E606" t="n">
         <v>2019.82</v>
       </c>
+      <c r="F606" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="607">
       <c r="A607" t="inlineStr">
@@ -13180,6 +15000,9 @@
       <c r="E607" t="n">
         <v>1139.82</v>
       </c>
+      <c r="F607" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="608">
       <c r="A608" t="inlineStr">
@@ -13201,6 +15024,9 @@
       <c r="E608" t="n">
         <v>1914.9519</v>
       </c>
+      <c r="F608" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="609">
       <c r="A609" t="inlineStr">
@@ -13222,6 +15048,9 @@
       <c r="E609" t="n">
         <v>1995.8718</v>
       </c>
+      <c r="F609" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="610">
       <c r="A610" t="inlineStr">
@@ -13243,6 +15072,9 @@
       <c r="E610" t="n">
         <v>1935.1446</v>
       </c>
+      <c r="F610" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="611">
       <c r="A611" t="inlineStr">
@@ -13264,6 +15096,9 @@
       <c r="E611" t="n">
         <v>2052.3048</v>
       </c>
+      <c r="F611" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="612">
       <c r="A612" t="inlineStr">
@@ -13285,6 +15120,9 @@
       <c r="E612" t="n">
         <v>2610.9021</v>
       </c>
+      <c r="F612" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="613">
       <c r="A613" t="inlineStr">
@@ -13306,6 +15144,9 @@
       <c r="E613" t="n">
         <v>3303.1995</v>
       </c>
+      <c r="F613" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="614">
       <c r="A614" t="inlineStr">
@@ -13327,6 +15168,9 @@
       <c r="E614" t="n">
         <v>2062.6499</v>
       </c>
+      <c r="F614" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="615">
       <c r="A615" t="inlineStr">
@@ -13348,6 +15192,9 @@
       <c r="E615" t="n">
         <v>3519.5344</v>
       </c>
+      <c r="F615" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="616">
       <c r="A616" t="inlineStr">
@@ -13369,6 +15216,9 @@
       <c r="E616" t="n">
         <v>1337.8869</v>
       </c>
+      <c r="F616" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="617">
       <c r="A617" t="inlineStr">
@@ -13390,6 +15240,9 @@
       <c r="E617" t="n">
         <v>1903.62</v>
       </c>
+      <c r="F617" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="618">
       <c r="A618" t="inlineStr">
@@ -13411,6 +15264,9 @@
       <c r="E618" t="n">
         <v>1860.0043</v>
       </c>
+      <c r="F618" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="619">
       <c r="A619" t="inlineStr">
@@ -13432,6 +15288,9 @@
       <c r="E619" t="n">
         <v>882.87</v>
       </c>
+      <c r="F619" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="620">
       <c r="A620" t="inlineStr">
@@ -13453,6 +15312,9 @@
       <c r="E620" t="n">
         <v>1000.82</v>
       </c>
+      <c r="F620" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="621">
       <c r="A621" t="inlineStr">
@@ -13474,6 +15336,9 @@
       <c r="E621" t="n">
         <v>1021.01</v>
       </c>
+      <c r="F621" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="622">
       <c r="A622" t="inlineStr">
@@ -13495,6 +15360,9 @@
       <c r="E622" t="n">
         <v>1214.82</v>
       </c>
+      <c r="F622" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="623">
       <c r="A623" t="inlineStr">
@@ -13516,6 +15384,9 @@
       <c r="E623" t="n">
         <v>1219.82</v>
       </c>
+      <c r="F623" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="624">
       <c r="A624" t="inlineStr">
@@ -13537,6 +15408,9 @@
       <c r="E624" t="n">
         <v>1215.82</v>
       </c>
+      <c r="F624" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="625">
       <c r="A625" t="inlineStr">
@@ -13558,6 +15432,9 @@
       <c r="E625" t="n">
         <v>1299.4709</v>
       </c>
+      <c r="F625" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="626">
       <c r="A626" t="inlineStr">
@@ -13579,6 +15456,9 @@
       <c r="E626" t="n">
         <v>1301.872</v>
       </c>
+      <c r="F626" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="627">
       <c r="A627" t="inlineStr">
@@ -13600,6 +15480,9 @@
       <c r="E627" t="n">
         <v>1364.82</v>
       </c>
+      <c r="F627" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="628">
       <c r="A628" t="inlineStr">
@@ -13621,6 +15504,9 @@
       <c r="E628" t="n">
         <v>1214.82</v>
       </c>
+      <c r="F628" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="629">
       <c r="A629" t="inlineStr">
@@ -13642,6 +15528,9 @@
       <c r="E629" t="n">
         <v>1853.42</v>
       </c>
+      <c r="F629" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="630">
       <c r="A630" t="inlineStr">
@@ -13663,6 +15552,9 @@
       <c r="E630" t="n">
         <v>2624.9228</v>
       </c>
+      <c r="F630" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="631">
       <c r="A631" t="inlineStr">
@@ -13684,6 +15576,9 @@
       <c r="E631" t="n">
         <v>2541.97</v>
       </c>
+      <c r="F631" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="632">
       <c r="A632" t="inlineStr">
@@ -13705,6 +15600,9 @@
       <c r="E632" t="n">
         <v>2540.97</v>
       </c>
+      <c r="F632" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="633">
       <c r="A633" t="inlineStr">
@@ -13726,6 +15624,9 @@
       <c r="E633" t="n">
         <v>2638.8324</v>
       </c>
+      <c r="F633" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="634">
       <c r="A634" t="inlineStr">
@@ -13747,6 +15648,9 @@
       <c r="E634" t="n">
         <v>2672.513</v>
       </c>
+      <c r="F634" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="635">
       <c r="A635" t="inlineStr">
@@ -13768,6 +15672,9 @@
       <c r="E635" t="n">
         <v>2451.0173</v>
       </c>
+      <c r="F635" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="636">
       <c r="A636" t="inlineStr">
@@ -13789,6 +15696,9 @@
       <c r="E636" t="n">
         <v>2473.9792</v>
       </c>
+      <c r="F636" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="637">
       <c r="A637" t="inlineStr">
@@ -13810,6 +15720,9 @@
       <c r="E637" t="n">
         <v>2550.2386</v>
       </c>
+      <c r="F637" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="638">
       <c r="A638" t="inlineStr">
@@ -13831,6 +15744,9 @@
       <c r="E638" t="n">
         <v>2866.269</v>
       </c>
+      <c r="F638" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="639">
       <c r="A639" t="inlineStr">
@@ -13852,6 +15768,9 @@
       <c r="E639" t="n">
         <v>2721.8746</v>
       </c>
+      <c r="F639" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="640">
       <c r="A640" t="inlineStr">
@@ -13873,6 +15792,9 @@
       <c r="E640" t="n">
         <v>2723.9694</v>
       </c>
+      <c r="F640" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="641">
       <c r="A641" t="inlineStr">
@@ -13894,6 +15816,9 @@
       <c r="E641" t="n">
         <v>2857.1133</v>
       </c>
+      <c r="F641" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="642">
       <c r="A642" t="inlineStr">
@@ -13915,6 +15840,9 @@
       <c r="E642" t="n">
         <v>2730.6366</v>
       </c>
+      <c r="F642" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="643">
       <c r="A643" t="inlineStr">
@@ -13936,6 +15864,9 @@
       <c r="E643" t="n">
         <v>2869.9451</v>
       </c>
+      <c r="F643" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="644">
       <c r="A644" t="inlineStr">
@@ -13957,6 +15888,9 @@
       <c r="E644" t="n">
         <v>2729.6366</v>
       </c>
+      <c r="F644" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="645">
       <c r="A645" t="inlineStr">
@@ -13978,6 +15912,9 @@
       <c r="E645" t="n">
         <v>2724.7545</v>
       </c>
+      <c r="F645" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="646">
       <c r="A646" t="inlineStr">
@@ -13999,6 +15936,9 @@
       <c r="E646" t="n">
         <v>3163.3889</v>
       </c>
+      <c r="F646" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="647">
       <c r="A647" t="inlineStr">
@@ -14020,6 +15960,9 @@
       <c r="E647" t="n">
         <v>3246.8091</v>
       </c>
+      <c r="F647" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="648">
       <c r="A648" t="inlineStr">
@@ -14041,6 +15984,9 @@
       <c r="E648" t="n">
         <v>4019.2061</v>
       </c>
+      <c r="F648" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="649">
       <c r="A649" t="inlineStr">
@@ -14062,6 +16008,9 @@
       <c r="E649" t="n">
         <v>1227.47</v>
       </c>
+      <c r="F649" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="650">
       <c r="A650" t="inlineStr">
@@ -14083,6 +16032,9 @@
       <c r="E650" t="n">
         <v>2056.8207</v>
       </c>
+      <c r="F650" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="651">
       <c r="A651" t="inlineStr">
@@ -14104,6 +16056,9 @@
       <c r="E651" t="n">
         <v>2544.5333</v>
       </c>
+      <c r="F651" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="652">
       <c r="A652" t="inlineStr">
@@ -14125,6 +16080,9 @@
       <c r="E652" t="n">
         <v>2544.5333</v>
       </c>
+      <c r="F652" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="653">
       <c r="A653" t="inlineStr">
@@ -14146,6 +16104,9 @@
       <c r="E653" t="n">
         <v>4901.603599999999</v>
       </c>
+      <c r="F653" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="654">
       <c r="A654" t="inlineStr">
@@ -14167,6 +16128,9 @@
       <c r="E654" t="n">
         <v>1959.9955</v>
       </c>
+      <c r="F654" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="655">
       <c r="A655" t="inlineStr">
@@ -14188,6 +16152,9 @@
       <c r="E655" t="n">
         <v>2109.5963</v>
       </c>
+      <c r="F655" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="656">
       <c r="A656" t="inlineStr">
@@ -14209,6 +16176,9 @@
       <c r="E656" t="n">
         <v>1958.3757</v>
       </c>
+      <c r="F656" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="657">
       <c r="A657" t="inlineStr">
@@ -14230,6 +16200,9 @@
       <c r="E657" t="n">
         <v>2979.0203</v>
       </c>
+      <c r="F657" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="658">
       <c r="A658" t="inlineStr">
@@ -14251,6 +16224,9 @@
       <c r="E658" t="n">
         <v>439.3</v>
       </c>
+      <c r="F658" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="659">
       <c r="A659" t="inlineStr">
@@ -14272,6 +16248,9 @@
       <c r="E659" t="n">
         <v>1186.62</v>
       </c>
+      <c r="F659" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="660">
       <c r="A660" t="inlineStr">
@@ -14293,6 +16272,9 @@
       <c r="E660" t="n">
         <v>4309.3201</v>
       </c>
+      <c r="F660" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="661">
       <c r="A661" t="inlineStr">
@@ -14314,6 +16296,9 @@
       <c r="E661" t="n">
         <v>3294.4044</v>
       </c>
+      <c r="F661" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="662">
       <c r="A662" t="inlineStr">
@@ -14335,6 +16320,9 @@
       <c r="E662" t="n">
         <v>1153.47</v>
       </c>
+      <c r="F662" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="663">
       <c r="A663" t="inlineStr">
@@ -14356,6 +16344,9 @@
       <c r="E663" t="n">
         <v>1227.47</v>
       </c>
+      <c r="F663" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="664">
       <c r="A664" t="inlineStr">
@@ -14377,6 +16368,9 @@
       <c r="E664" t="n">
         <v>1255.2341</v>
       </c>
+      <c r="F664" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="665">
       <c r="A665" t="inlineStr">
@@ -14398,6 +16392,9 @@
       <c r="E665" t="n">
         <v>1172.66</v>
       </c>
+      <c r="F665" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="666">
       <c r="A666" t="inlineStr">
@@ -14419,6 +16416,9 @@
       <c r="E666" t="n">
         <v>1620.5275</v>
       </c>
+      <c r="F666" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="667">
       <c r="A667" t="inlineStr">
@@ -14440,6 +16440,9 @@
       <c r="E667" t="n">
         <v>2372.8999</v>
       </c>
+      <c r="F667" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="668">
       <c r="A668" t="inlineStr">
@@ -14461,6 +16464,9 @@
       <c r="E668" t="n">
         <v>2946.8166</v>
       </c>
+      <c r="F668" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="669">
       <c r="A669" t="inlineStr">
@@ -14482,6 +16488,9 @@
       <c r="E669" t="n">
         <v>2053.2347</v>
       </c>
+      <c r="F669" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="670">
       <c r="A670" t="inlineStr">
@@ -14503,6 +16512,9 @@
       <c r="E670" t="n">
         <v>5063.934999999999</v>
       </c>
+      <c r="F670" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="671">
       <c r="A671" t="inlineStr">
@@ -14524,6 +16536,9 @@
       <c r="E671" t="n">
         <v>2469.5333</v>
       </c>
+      <c r="F671" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="672">
       <c r="A672" t="inlineStr">
@@ -14545,6 +16560,9 @@
       <c r="E672" t="n">
         <v>3886.6933</v>
       </c>
+      <c r="F672" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="673">
       <c r="A673" t="inlineStr">
@@ -14566,6 +16584,9 @@
       <c r="E673" t="n">
         <v>1304.45</v>
       </c>
+      <c r="F673" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="674">
       <c r="A674" t="inlineStr">
@@ -14587,6 +16608,9 @@
       <c r="E674" t="n">
         <v>1901.2121</v>
       </c>
+      <c r="F674" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="675">
       <c r="A675" t="inlineStr">
@@ -14608,6 +16632,9 @@
       <c r="E675" t="n">
         <v>2762.8668</v>
       </c>
+      <c r="F675" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="676">
       <c r="A676" t="inlineStr">
@@ -14629,6 +16656,9 @@
       <c r="E676" t="n">
         <v>1289.5333</v>
       </c>
+      <c r="F676" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="677">
       <c r="A677" t="inlineStr">
@@ -14650,6 +16680,9 @@
       <c r="E677" t="n">
         <v>1977.0179</v>
       </c>
+      <c r="F677" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="678">
       <c r="A678" t="inlineStr">
@@ -14671,6 +16704,9 @@
       <c r="E678" t="n">
         <v>1853.5083</v>
       </c>
+      <c r="F678" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="679">
       <c r="A679" t="inlineStr">
@@ -14692,6 +16728,9 @@
       <c r="E679" t="n">
         <v>2626.3968</v>
       </c>
+      <c r="F679" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="680">
       <c r="A680" t="inlineStr">
@@ -14713,6 +16752,9 @@
       <c r="E680" t="n">
         <v>1918.4015</v>
       </c>
+      <c r="F680" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="681">
       <c r="A681" t="inlineStr">
@@ -14734,6 +16776,9 @@
       <c r="E681" t="n">
         <v>1897.0809</v>
       </c>
+      <c r="F681" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="682">
       <c r="A682" t="inlineStr">
@@ -14755,6 +16800,9 @@
       <c r="E682" t="n">
         <v>2585.9866</v>
       </c>
+      <c r="F682" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="683">
       <c r="A683" t="inlineStr">
@@ -14776,6 +16824,9 @@
       <c r="E683" t="n">
         <v>3287.0137</v>
       </c>
+      <c r="F683" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="684">
       <c r="A684" t="inlineStr">
@@ -14797,6 +16848,9 @@
       <c r="E684" t="n">
         <v>3204.5366</v>
       </c>
+      <c r="F684" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="685">
       <c r="A685" t="inlineStr">
@@ -14818,6 +16872,9 @@
       <c r="E685" t="n">
         <v>3220.9121</v>
       </c>
+      <c r="F685" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="686">
       <c r="A686" t="inlineStr">
@@ -14839,6 +16896,9 @@
       <c r="E686" t="n">
         <v>5127.4737</v>
       </c>
+      <c r="F686" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="687">
       <c r="A687" t="inlineStr">
@@ -14860,6 +16920,9 @@
       <c r="E687" t="n">
         <v>3377.4714</v>
       </c>
+      <c r="F687" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="688">
       <c r="A688" t="inlineStr">
@@ -14881,6 +16944,9 @@
       <c r="E688" t="n">
         <v>3799.6812</v>
       </c>
+      <c r="F688" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="689">
       <c r="A689" t="inlineStr">
@@ -14902,6 +16968,9 @@
       <c r="E689" t="n">
         <v>3671.7302</v>
       </c>
+      <c r="F689" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="690">
       <c r="A690" t="inlineStr">
@@ -14923,6 +16992,9 @@
       <c r="E690" t="n">
         <v>3237.5777</v>
       </c>
+      <c r="F690" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="691">
       <c r="A691" t="inlineStr">
@@ -14944,6 +17016,9 @@
       <c r="E691" t="n">
         <v>1724.67</v>
       </c>
+      <c r="F691" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="692">
       <c r="A692" t="inlineStr">
@@ -14965,6 +17040,9 @@
       <c r="E692" t="n">
         <v>1202.4328</v>
       </c>
+      <c r="F692" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="693">
       <c r="A693" t="inlineStr">
@@ -14986,6 +17064,9 @@
       <c r="E693" t="n">
         <v>2447.45</v>
       </c>
+      <c r="F693" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="694">
       <c r="A694" t="inlineStr">
@@ -15007,6 +17088,9 @@
       <c r="E694" t="n">
         <v>2224.3559</v>
       </c>
+      <c r="F694" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="695">
       <c r="A695" t="inlineStr">
@@ -15028,6 +17112,9 @@
       <c r="E695" t="n">
         <v>3429.32</v>
       </c>
+      <c r="F695" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="696">
       <c r="A696" t="inlineStr">
@@ -15049,6 +17136,9 @@
       <c r="E696" t="n">
         <v>5826.95</v>
       </c>
+      <c r="F696" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="697">
       <c r="A697" t="inlineStr">
@@ -15070,6 +17160,9 @@
       <c r="E697" t="n">
         <v>2222.45</v>
       </c>
+      <c r="F697" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="698">
       <c r="A698" t="inlineStr">
@@ -15091,6 +17184,9 @@
       <c r="E698" t="n">
         <v>3193.7702</v>
       </c>
+      <c r="F698" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="699">
       <c r="A699" t="inlineStr">
@@ -15112,6 +17208,9 @@
       <c r="E699" t="n">
         <v>3524.6179</v>
       </c>
+      <c r="F699" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="700">
       <c r="A700" t="inlineStr">
@@ -15133,6 +17232,9 @@
       <c r="E700" t="n">
         <v>4815.6346</v>
       </c>
+      <c r="F700" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="701">
       <c r="A701" t="inlineStr">
@@ -15154,6 +17256,9 @@
       <c r="E701" t="n">
         <v>2474.9792</v>
       </c>
+      <c r="F701" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="702">
       <c r="A702" t="inlineStr">
@@ -15175,6 +17280,9 @@
       <c r="E702" t="n">
         <v>2046.6858</v>
       </c>
+      <c r="F702" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="703">
       <c r="A703" t="inlineStr">
@@ -15196,6 +17304,9 @@
       <c r="E703" t="n">
         <v>2863.1968</v>
       </c>
+      <c r="F703" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="704">
       <c r="A704" t="inlineStr">
@@ -15217,6 +17328,9 @@
       <c r="E704" t="n">
         <v>3187.3485</v>
       </c>
+      <c r="F704" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="705">
       <c r="A705" t="inlineStr">
@@ -15238,6 +17352,9 @@
       <c r="E705" t="n">
         <v>4213.9833</v>
       </c>
+      <c r="F705" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="706">
       <c r="A706" t="inlineStr">
@@ -15259,6 +17376,9 @@
       <c r="E706" t="n">
         <v>3225.6153</v>
       </c>
+      <c r="F706" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="707">
       <c r="A707" t="inlineStr">
@@ -15280,6 +17400,9 @@
       <c r="E707" t="n">
         <v>4176.931399999999</v>
       </c>
+      <c r="F707" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="708">
       <c r="A708" t="inlineStr">
@@ -15301,6 +17424,9 @@
       <c r="E708" t="n">
         <v>4031.3266</v>
       </c>
+      <c r="F708" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="709">
       <c r="A709" t="inlineStr">
@@ -15322,6 +17448,9 @@
       <c r="E709" t="n">
         <v>3404.2316</v>
       </c>
+      <c r="F709" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="710">
       <c r="A710" t="inlineStr">
@@ -15343,6 +17472,9 @@
       <c r="E710" t="n">
         <v>3365.2502</v>
       </c>
+      <c r="F710" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="711">
       <c r="A711" t="inlineStr">
@@ -15364,6 +17496,9 @@
       <c r="E711" t="n">
         <v>2822.3921</v>
       </c>
+      <c r="F711" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="712">
       <c r="A712" t="inlineStr">
@@ -15385,6 +17520,9 @@
       <c r="E712" t="n">
         <v>3221.8114</v>
       </c>
+      <c r="F712" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="713">
       <c r="A713" t="inlineStr">
@@ -15406,6 +17544,9 @@
       <c r="E713" t="n">
         <v>2552.1688</v>
       </c>
+      <c r="F713" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="714">
       <c r="A714" t="inlineStr">
@@ -15427,6 +17568,9 @@
       <c r="E714" t="n">
         <v>2570.5574</v>
       </c>
+      <c r="F714" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="715">
       <c r="A715" t="inlineStr">
@@ -15448,6 +17592,9 @@
       <c r="E715" t="n">
         <v>2584.1044</v>
       </c>
+      <c r="F715" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="716">
       <c r="A716" t="inlineStr">
@@ -15469,6 +17616,9 @@
       <c r="E716" t="n">
         <v>3191.5074</v>
       </c>
+      <c r="F716" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="717">
       <c r="A717" t="inlineStr">
@@ -15490,6 +17640,9 @@
       <c r="E717" t="n">
         <v>3536.8738</v>
       </c>
+      <c r="F717" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="718">
       <c r="A718" t="inlineStr">
@@ -15511,6 +17664,9 @@
       <c r="E718" t="n">
         <v>3184.1638</v>
       </c>
+      <c r="F718" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="719">
       <c r="A719" t="inlineStr">
@@ -15532,6 +17688,9 @@
       <c r="E719" t="n">
         <v>2525.2574</v>
       </c>
+      <c r="F719" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="720">
       <c r="A720" t="inlineStr">
@@ -15553,6 +17712,9 @@
       <c r="E720" t="n">
         <v>2531.9176</v>
       </c>
+      <c r="F720" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="721">
       <c r="A721" t="inlineStr">
@@ -15574,6 +17736,9 @@
       <c r="E721" t="n">
         <v>2488.6599</v>
       </c>
+      <c r="F721" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="722">
       <c r="A722" t="inlineStr">
@@ -15595,6 +17760,9 @@
       <c r="E722" t="n">
         <v>3262.4825</v>
       </c>
+      <c r="F722" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="723">
       <c r="A723" t="inlineStr">
@@ -15616,6 +17784,9 @@
       <c r="E723" t="n">
         <v>2364.9263</v>
       </c>
+      <c r="F723" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="724">
       <c r="A724" t="inlineStr">
@@ -15637,6 +17808,9 @@
       <c r="E724" t="n">
         <v>1797.7348</v>
       </c>
+      <c r="F724" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="725">
       <c r="A725" t="inlineStr">
@@ -15658,6 +17832,9 @@
       <c r="E725" t="n">
         <v>2418.6848</v>
       </c>
+      <c r="F725" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="726">
       <c r="A726" t="inlineStr">
@@ -15679,6 +17856,9 @@
       <c r="E726" t="n">
         <v>2690.7584</v>
       </c>
+      <c r="F726" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="727">
       <c r="A727" t="inlineStr">
@@ -15700,6 +17880,9 @@
       <c r="E727" t="n">
         <v>2891.1669</v>
       </c>
+      <c r="F727" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="728">
       <c r="A728" t="inlineStr">
@@ -15721,6 +17904,9 @@
       <c r="E728" t="n">
         <v>4432.2897</v>
       </c>
+      <c r="F728" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="729">
       <c r="A729" t="inlineStr">
@@ -15742,6 +17928,9 @@
       <c r="E729" t="n">
         <v>3906.6307</v>
       </c>
+      <c r="F729" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="730">
       <c r="A730" t="inlineStr">
@@ -15763,6 +17952,9 @@
       <c r="E730" t="n">
         <v>3632.3248</v>
       </c>
+      <c r="F730" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="731">
       <c r="A731" t="inlineStr">
@@ -15784,6 +17976,9 @@
       <c r="E731" t="n">
         <v>1987.5377</v>
       </c>
+      <c r="F731" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="732">
       <c r="A732" t="inlineStr">
@@ -15805,6 +18000,9 @@
       <c r="E732" t="n">
         <v>2371.4614</v>
       </c>
+      <c r="F732" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="733">
       <c r="A733" t="inlineStr">
@@ -15826,6 +18024,9 @@
       <c r="E733" t="n">
         <v>2628.8944</v>
       </c>
+      <c r="F733" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="734">
       <c r="A734" t="inlineStr">
@@ -15847,6 +18048,9 @@
       <c r="E734" t="n">
         <v>2545.9416</v>
       </c>
+      <c r="F734" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="735">
       <c r="A735" t="inlineStr">
@@ -15868,6 +18072,9 @@
       <c r="E735" t="n">
         <v>2618.2184</v>
       </c>
+      <c r="F735" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="736">
       <c r="A736" t="inlineStr">
@@ -15889,6 +18096,9 @@
       <c r="E736" t="n">
         <v>2565.9476</v>
       </c>
+      <c r="F736" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="737">
       <c r="A737" t="inlineStr">
@@ -15910,6 +18120,9 @@
       <c r="E737" t="n">
         <v>2446.4614</v>
       </c>
+      <c r="F737" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="738">
       <c r="A738" t="inlineStr">
@@ -15931,6 +18144,9 @@
       <c r="E738" t="n">
         <v>2573.2402</v>
       </c>
+      <c r="F738" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="739">
       <c r="A739" t="inlineStr">
@@ -15952,6 +18168,9 @@
       <c r="E739" t="n">
         <v>2493.6599</v>
       </c>
+      <c r="F739" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="740">
       <c r="A740" t="inlineStr">
@@ -15973,6 +18192,9 @@
       <c r="E740" t="n">
         <v>2638.4876</v>
       </c>
+      <c r="F740" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="741">
       <c r="A741" t="inlineStr">
@@ -15994,6 +18216,9 @@
       <c r="E741" t="n">
         <v>3268.7999</v>
       </c>
+      <c r="F741" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="742">
       <c r="A742" t="inlineStr">
@@ -16015,6 +18240,9 @@
       <c r="E742" t="n">
         <v>2863.8699</v>
       </c>
+      <c r="F742" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="743">
       <c r="A743" t="inlineStr">
@@ -16036,6 +18264,9 @@
       <c r="E743" t="n">
         <v>3255.1669</v>
       </c>
+      <c r="F743" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="744">
       <c r="A744" t="inlineStr">
@@ -16057,6 +18288,9 @@
       <c r="E744" t="n">
         <v>3248.8162</v>
       </c>
+      <c r="F744" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="745">
       <c r="A745" t="inlineStr">
@@ -16078,6 +18312,9 @@
       <c r="E745" t="n">
         <v>3253.8185</v>
       </c>
+      <c r="F745" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="746">
       <c r="A746" t="inlineStr">
@@ -16099,6 +18336,9 @@
       <c r="E746" t="n">
         <v>2551.8254</v>
       </c>
+      <c r="F746" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="747">
       <c r="A747" t="inlineStr">
@@ -16120,6 +18360,9 @@
       <c r="E747" t="n">
         <v>2468.2184</v>
       </c>
+      <c r="F747" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="748">
       <c r="A748" t="inlineStr">
@@ -16141,6 +18384,9 @@
       <c r="E748" t="n">
         <v>2546.8254</v>
       </c>
+      <c r="F748" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="749">
       <c r="A749" t="inlineStr">
@@ -16162,6 +18408,9 @@
       <c r="E749" t="n">
         <v>4024.4545</v>
       </c>
+      <c r="F749" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="750">
       <c r="A750" t="inlineStr">
@@ -16183,6 +18432,9 @@
       <c r="E750" t="n">
         <v>5020.8231</v>
       </c>
+      <c r="F750" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="751">
       <c r="A751" t="inlineStr">
@@ -16204,6 +18456,9 @@
       <c r="E751" t="n">
         <v>3425.6902</v>
       </c>
+      <c r="F751" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="752">
       <c r="A752" t="inlineStr">
@@ -16225,6 +18480,9 @@
       <c r="E752" t="n">
         <v>2255.4994</v>
       </c>
+      <c r="F752" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="753">
       <c r="A753" t="inlineStr">
@@ -16246,6 +18504,9 @@
       <c r="E753" t="n">
         <v>2308.3962</v>
       </c>
+      <c r="F753" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="754">
       <c r="A754" t="inlineStr">
@@ -16267,6 +18528,9 @@
       <c r="E754" t="n">
         <v>3717.4924</v>
       </c>
+      <c r="F754" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="755">
       <c r="A755" t="inlineStr">
@@ -16288,6 +18552,9 @@
       <c r="E755" t="n">
         <v>2813.8378</v>
       </c>
+      <c r="F755" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="756">
       <c r="A756" t="inlineStr">
@@ -16309,6 +18576,9 @@
       <c r="E756" t="n">
         <v>4523.8503</v>
       </c>
+      <c r="F756" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="757">
       <c r="A757" t="inlineStr">
@@ -16330,6 +18600,9 @@
       <c r="E757" t="n">
         <v>2776.2122</v>
       </c>
+      <c r="F757" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="758">
       <c r="A758" t="inlineStr">
@@ -16351,6 +18624,9 @@
       <c r="E758" t="n">
         <v>4361.2544</v>
       </c>
+      <c r="F758" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="759">
       <c r="A759" t="inlineStr">
@@ -16372,6 +18648,9 @@
       <c r="E759" t="n">
         <v>3673.2584</v>
       </c>
+      <c r="F759" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="760">
       <c r="A760" t="inlineStr">
@@ -16393,6 +18672,9 @@
       <c r="E760" t="n">
         <v>4062.2297</v>
       </c>
+      <c r="F760" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="761">
       <c r="A761" t="inlineStr">
@@ -16414,6 +18696,9 @@
       <c r="E761" t="n">
         <v>3499.6867</v>
       </c>
+      <c r="F761" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="762">
       <c r="A762" t="inlineStr">
@@ -16435,6 +18720,9 @@
       <c r="E762" t="n">
         <v>2705.6057</v>
       </c>
+      <c r="F762" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="763">
       <c r="A763" t="inlineStr">
@@ -16456,6 +18744,9 @@
       <c r="E763" t="n">
         <v>4673.215</v>
       </c>
+      <c r="F763" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="764">
       <c r="A764" t="inlineStr">
@@ -16477,6 +18768,9 @@
       <c r="E764" t="n">
         <v>2593.3328</v>
       </c>
+      <c r="F764" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="765">
       <c r="A765" t="inlineStr">
@@ -16498,6 +18792,9 @@
       <c r="E765" t="n">
         <v>2672.9569</v>
       </c>
+      <c r="F765" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="766">
       <c r="A766" t="inlineStr">
@@ -16519,6 +18816,9 @@
       <c r="E766" t="n">
         <v>3755.2678</v>
       </c>
+      <c r="F766" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="767">
       <c r="A767" t="inlineStr">
@@ -16540,6 +18840,9 @@
       <c r="E767" t="n">
         <v>2513.4442</v>
       </c>
+      <c r="F767" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="768">
       <c r="A768" t="inlineStr">
@@ -16561,6 +18864,9 @@
       <c r="E768" t="n">
         <v>3313.1456</v>
       </c>
+      <c r="F768" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="769">
       <c r="A769" t="inlineStr">
@@ -16582,6 +18888,9 @@
       <c r="E769" t="n">
         <v>2731.6054</v>
       </c>
+      <c r="F769" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="770">
       <c r="A770" t="inlineStr">
@@ -16603,6 +18912,9 @@
       <c r="E770" t="n">
         <v>1163.1099</v>
       </c>
+      <c r="F770" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="771">
       <c r="A771" t="inlineStr">
@@ -16624,6 +18936,9 @@
       <c r="E771" t="n">
         <v>1079.7374</v>
       </c>
+      <c r="F771" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="772">
       <c r="A772" t="inlineStr">
@@ -16645,6 +18960,9 @@
       <c r="E772" t="n">
         <v>1858.3641</v>
       </c>
+      <c r="F772" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="773">
       <c r="A773" t="inlineStr">
@@ -16666,6 +18984,9 @@
       <c r="E773" t="n">
         <v>1797.7099</v>
       </c>
+      <c r="F773" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="774">
       <c r="A774" t="inlineStr">
@@ -16687,6 +19008,9 @@
       <c r="E774" t="n">
         <v>1960.7374</v>
       </c>
+      <c r="F774" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="775">
       <c r="A775" t="inlineStr">
@@ -16708,6 +19032,9 @@
       <c r="E775" t="n">
         <v>2205.9409</v>
       </c>
+      <c r="F775" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="776">
       <c r="A776" t="inlineStr">
@@ -16729,6 +19056,9 @@
       <c r="E776" t="n">
         <v>2128.6599</v>
       </c>
+      <c r="F776" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="777">
       <c r="A777" t="inlineStr">
@@ -16750,6 +19080,9 @@
       <c r="E777" t="n">
         <v>2314.0355</v>
       </c>
+      <c r="F777" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="778">
       <c r="A778" t="inlineStr">
@@ -16771,6 +19104,9 @@
       <c r="E778" t="n">
         <v>2517.9353</v>
       </c>
+      <c r="F778" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="779">
       <c r="A779" t="inlineStr">
@@ -16792,6 +19128,9 @@
       <c r="E779" t="n">
         <v>2708.7314</v>
       </c>
+      <c r="F779" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="780">
       <c r="A780" t="inlineStr">
@@ -16813,6 +19152,9 @@
       <c r="E780" t="n">
         <v>3007.4014</v>
       </c>
+      <c r="F780" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="781">
       <c r="A781" t="inlineStr">
@@ -16834,6 +19176,9 @@
       <c r="E781" t="n">
         <v>1921.2162</v>
       </c>
+      <c r="F781" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="782">
       <c r="A782" t="inlineStr">
@@ -16855,6 +19200,9 @@
       <c r="E782" t="n">
         <v>2554.1163</v>
       </c>
+      <c r="F782" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="783">
       <c r="A783" t="inlineStr">
@@ -16876,6 +19224,9 @@
       <c r="E783" t="n">
         <v>2634.2138</v>
       </c>
+      <c r="F783" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="784">
       <c r="A784" t="inlineStr">
@@ -16897,6 +19248,9 @@
       <c r="E784" t="n">
         <v>2566.1547</v>
       </c>
+      <c r="F784" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="785">
       <c r="A785" t="inlineStr">
@@ -16918,6 +19272,9 @@
       <c r="E785" t="n">
         <v>2708.4394</v>
       </c>
+      <c r="F785" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="786">
       <c r="A786" t="inlineStr">
@@ -16939,6 +19296,9 @@
       <c r="E786" t="n">
         <v>2542.9723</v>
       </c>
+      <c r="F786" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="787">
       <c r="A787" t="inlineStr">
@@ -16960,6 +19320,9 @@
       <c r="E787" t="n">
         <v>3030.2178</v>
       </c>
+      <c r="F787" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="788">
       <c r="A788" t="inlineStr">
@@ -16981,6 +19344,9 @@
       <c r="E788" t="n">
         <v>3334.5636</v>
       </c>
+      <c r="F788" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="789">
       <c r="A789" t="inlineStr">
@@ -17002,6 +19368,9 @@
       <c r="E789" t="n">
         <v>3247.7642</v>
       </c>
+      <c r="F789" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="790">
       <c r="A790" t="inlineStr">
@@ -17023,6 +19392,9 @@
       <c r="E790" t="n">
         <v>3209.8596</v>
       </c>
+      <c r="F790" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="791">
       <c r="A791" t="inlineStr">
@@ -17044,6 +19416,9 @@
       <c r="E791" t="n">
         <v>3537.7578</v>
       </c>
+      <c r="F791" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="792">
       <c r="A792" t="inlineStr">
@@ -17065,6 +19440,9 @@
       <c r="E792" t="n">
         <v>2032.183</v>
       </c>
+      <c r="F792" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="793">
       <c r="A793" t="inlineStr">
@@ -17086,6 +19464,9 @@
       <c r="E793" t="n">
         <v>2627.2678</v>
       </c>
+      <c r="F793" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="794">
       <c r="A794" t="inlineStr">
@@ -17107,6 +19488,9 @@
       <c r="E794" t="n">
         <v>2491.1914</v>
       </c>
+      <c r="F794" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="795">
       <c r="A795" t="inlineStr">
@@ -17128,6 +19512,9 @@
       <c r="E795" t="n">
         <v>2542.7331</v>
       </c>
+      <c r="F795" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="796">
       <c r="A796" t="inlineStr">
@@ -17149,6 +19536,9 @@
       <c r="E796" t="n">
         <v>2483.5844</v>
       </c>
+      <c r="F796" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="797">
       <c r="A797" t="inlineStr">
@@ -17170,6 +19560,9 @@
       <c r="E797" t="n">
         <v>2495.0788</v>
       </c>
+      <c r="F797" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="798">
       <c r="A798" t="inlineStr">
@@ -17191,6 +19584,9 @@
       <c r="E798" t="n">
         <v>1914.8082</v>
       </c>
+      <c r="F798" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="799">
       <c r="A799" t="inlineStr">
@@ -17212,6 +19608,9 @@
       <c r="E799" t="n">
         <v>2678.2905</v>
       </c>
+      <c r="F799" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="800">
       <c r="A800" t="inlineStr">
@@ -17233,6 +19632,9 @@
       <c r="E800" t="n">
         <v>3956.8925</v>
       </c>
+      <c r="F800" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="801">
       <c r="A801" t="inlineStr">
@@ -17254,6 +19656,9 @@
       <c r="E801" t="n">
         <v>2386.27</v>
       </c>
+      <c r="F801" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="802">
       <c r="A802" t="inlineStr">
@@ -17275,6 +19680,9 @@
       <c r="E802" t="n">
         <v>2442.0294</v>
       </c>
+      <c r="F802" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="803">
       <c r="A803" t="inlineStr">
@@ -17296,6 +19704,9 @@
       <c r="E803" t="n">
         <v>3148.7519</v>
       </c>
+      <c r="F803" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="804">
       <c r="A804" t="inlineStr">
@@ -17317,6 +19728,9 @@
       <c r="E804" t="n">
         <v>4444.2262</v>
       </c>
+      <c r="F804" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="805">
       <c r="A805" t="inlineStr">
@@ -17338,6 +19752,9 @@
       <c r="E805" t="n">
         <v>4479.8914</v>
       </c>
+      <c r="F805" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="806">
       <c r="A806" t="inlineStr">
@@ -17359,6 +19776,9 @@
       <c r="E806" t="n">
         <v>4419.902099999999</v>
       </c>
+      <c r="F806" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="807">
       <c r="A807" t="inlineStr">
@@ -17380,6 +19800,9 @@
       <c r="E807" t="n">
         <v>3988.9066</v>
       </c>
+      <c r="F807" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="808">
       <c r="A808" t="inlineStr">
@@ -17401,6 +19824,9 @@
       <c r="E808" t="n">
         <v>3334.9304</v>
       </c>
+      <c r="F808" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="809">
       <c r="A809" t="inlineStr">
@@ -17422,6 +19848,9 @@
       <c r="E809" t="n">
         <v>3219.7854</v>
       </c>
+      <c r="F809" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="810">
       <c r="A810" t="inlineStr">
@@ -17443,6 +19872,9 @@
       <c r="E810" t="n">
         <v>4664.4013</v>
       </c>
+      <c r="F810" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="811">
       <c r="A811" t="inlineStr">
@@ -17464,6 +19896,9 @@
       <c r="E811" t="n">
         <v>4765.9581</v>
       </c>
+      <c r="F811" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="812">
       <c r="A812" t="inlineStr">
@@ -17485,6 +19920,9 @@
       <c r="E812" t="n">
         <v>5976.6148</v>
       </c>
+      <c r="F812" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="813">
       <c r="A813" t="inlineStr">
@@ -17506,6 +19944,9 @@
       <c r="E813" t="n">
         <v>2666.2627</v>
       </c>
+      <c r="F813" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="814">
       <c r="A814" t="inlineStr">
@@ -17527,6 +19968,9 @@
       <c r="E814" t="n">
         <v>2736.6843</v>
       </c>
+      <c r="F814" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="815">
       <c r="A815" t="inlineStr">
@@ -17548,6 +19992,9 @@
       <c r="E815" t="n">
         <v>2184.1852</v>
       </c>
+      <c r="F815" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="816">
       <c r="A816" t="inlineStr">
@@ -17569,6 +20016,9 @@
       <c r="E816" t="n">
         <v>4356.2196</v>
       </c>
+      <c r="F816" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="817">
       <c r="A817" t="inlineStr">
@@ -17590,6 +20040,9 @@
       <c r="E817" t="n">
         <v>4317.3558</v>
       </c>
+      <c r="F817" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="818">
       <c r="A818" t="inlineStr">
@@ -17611,6 +20064,9 @@
       <c r="E818" t="n">
         <v>389.7872</v>
       </c>
+      <c r="F818" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="819">
       <c r="A819" t="inlineStr">
@@ -17632,6 +20088,9 @@
       <c r="E819" t="n">
         <v>1270.0022</v>
       </c>
+      <c r="F819" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="820">
       <c r="A820" t="inlineStr">
@@ -17653,6 +20112,9 @@
       <c r="E820" t="n">
         <v>2701.2474</v>
       </c>
+      <c r="F820" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="821">
       <c r="A821" t="inlineStr">
@@ -17674,6 +20136,9 @@
       <c r="E821" t="n">
         <v>1813.0816</v>
       </c>
+      <c r="F821" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="822">
       <c r="A822" t="inlineStr">
@@ -17695,6 +20160,9 @@
       <c r="E822" t="n">
         <v>1866.6344</v>
       </c>
+      <c r="F822" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="823">
       <c r="A823" t="inlineStr">
@@ -17716,6 +20184,9 @@
       <c r="E823" t="n">
         <v>1861.3912</v>
       </c>
+      <c r="F823" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="824">
       <c r="A824" t="inlineStr">
@@ -17737,6 +20208,9 @@
       <c r="E824" t="n">
         <v>2054.4816</v>
       </c>
+      <c r="F824" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="825">
       <c r="A825" t="inlineStr">
@@ -17758,6 +20232,9 @@
       <c r="E825" t="n">
         <v>2194.2821</v>
       </c>
+      <c r="F825" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="826">
       <c r="A826" t="inlineStr">
@@ -17779,6 +20256,9 @@
       <c r="E826" t="n">
         <v>3930.55</v>
       </c>
+      <c r="F826" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="827">
       <c r="A827" t="inlineStr">
@@ -17800,6 +20280,9 @@
       <c r="E827" t="n">
         <v>3780.55</v>
       </c>
+      <c r="F827" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="828">
       <c r="A828" t="inlineStr">
@@ -17821,6 +20304,9 @@
       <c r="E828" t="n">
         <v>4693.0346</v>
       </c>
+      <c r="F828" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="829">
       <c r="A829" t="inlineStr">
@@ -17842,6 +20328,9 @@
       <c r="E829" t="n">
         <v>2098.9833</v>
       </c>
+      <c r="F829" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="830">
       <c r="A830" t="inlineStr">
@@ -17863,6 +20352,9 @@
       <c r="E830" t="n">
         <v>2160.93</v>
       </c>
+      <c r="F830" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="831">
       <c r="A831" t="inlineStr">
@@ -17884,6 +20376,9 @@
       <c r="E831" t="n">
         <v>2098.9833</v>
       </c>
+      <c r="F831" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="832">
       <c r="A832" t="inlineStr">
@@ -17905,6 +20400,9 @@
       <c r="E832" t="n">
         <v>3335.93</v>
       </c>
+      <c r="F832" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="833">
       <c r="A833" t="inlineStr">
@@ -17926,6 +20424,9 @@
       <c r="E833" t="n">
         <v>3542.28</v>
       </c>
+      <c r="F833" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="834">
       <c r="A834" t="inlineStr">
@@ -17947,6 +20448,9 @@
       <c r="E834" t="n">
         <v>2862.4652</v>
       </c>
+      <c r="F834" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="835">
       <c r="A835" t="inlineStr">
@@ -17968,6 +20472,9 @@
       <c r="E835" t="n">
         <v>5515.5693</v>
       </c>
+      <c r="F835" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="836">
       <c r="A836" t="inlineStr">
@@ -17989,6 +20496,9 @@
       <c r="E836" t="n">
         <v>3520.3346</v>
       </c>
+      <c r="F836" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="837">
       <c r="A837" t="inlineStr">
@@ -18010,6 +20520,9 @@
       <c r="E837" t="n">
         <v>2943.2669</v>
       </c>
+      <c r="F837" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="838">
       <c r="A838" t="inlineStr">
@@ -18031,6 +20544,9 @@
       <c r="E838" t="n">
         <v>2862.3497</v>
       </c>
+      <c r="F838" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="839">
       <c r="A839" t="inlineStr">
@@ -18052,6 +20568,9 @@
       <c r="E839" t="n">
         <v>3705.7515</v>
       </c>
+      <c r="F839" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="840">
       <c r="A840" t="inlineStr">
@@ -18073,6 +20592,9 @@
       <c r="E840" t="n">
         <v>2795.3737</v>
       </c>
+      <c r="F840" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="841">
       <c r="A841" t="inlineStr">
@@ -18094,6 +20616,9 @@
       <c r="E841" t="n">
         <v>4808.9938</v>
       </c>
+      <c r="F841" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="842">
       <c r="A842" t="inlineStr">
@@ -18115,6 +20640,9 @@
       <c r="E842" t="n">
         <v>3926.6296</v>
       </c>
+      <c r="F842" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="843">
       <c r="A843" t="inlineStr">
@@ -18136,6 +20664,9 @@
       <c r="E843" t="n">
         <v>4531.1218</v>
       </c>
+      <c r="F843" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="844">
       <c r="A844" t="inlineStr">
@@ -18157,6 +20688,9 @@
       <c r="E844" t="n">
         <v>4450.2019</v>
       </c>
+      <c r="F844" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="845">
       <c r="A845" t="inlineStr">
@@ -18178,6 +20712,9 @@
       <c r="E845" t="n">
         <v>2506.0324</v>
       </c>
+      <c r="F845" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="846">
       <c r="A846" t="inlineStr">
@@ -18199,6 +20736,9 @@
       <c r="E846" t="n">
         <v>2532.8449</v>
       </c>
+      <c r="F846" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="847">
       <c r="A847" t="inlineStr">
@@ -18220,6 +20760,9 @@
       <c r="E847" t="n">
         <v>3304.0835</v>
       </c>
+      <c r="F847" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="848">
       <c r="A848" t="inlineStr">
@@ -18241,6 +20784,9 @@
       <c r="E848" t="n">
         <v>3360.9407</v>
       </c>
+      <c r="F848" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="849">
       <c r="A849" t="inlineStr">
@@ -18262,6 +20808,9 @@
       <c r="E849" t="n">
         <v>3576.0368</v>
       </c>
+      <c r="F849" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="850">
       <c r="A850" t="inlineStr">
@@ -18283,6 +20832,9 @@
       <c r="E850" t="n">
         <v>3538.9423</v>
       </c>
+      <c r="F850" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="851">
       <c r="A851" t="inlineStr">
@@ -18304,6 +20856,9 @@
       <c r="E851" t="n">
         <v>2775.0431</v>
       </c>
+      <c r="F851" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="852">
       <c r="A852" t="inlineStr">
@@ -18325,6 +20880,9 @@
       <c r="E852" t="n">
         <v>4688.3847</v>
       </c>
+      <c r="F852" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="853">
       <c r="A853" t="inlineStr">
@@ -18346,6 +20904,9 @@
       <c r="E853" t="n">
         <v>968.7746</v>
       </c>
+      <c r="F853" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="854">
       <c r="A854" t="inlineStr">
@@ -18367,6 +20928,9 @@
       <c r="E854" t="n">
         <v>6074.5264</v>
       </c>
+      <c r="F854" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="855">
       <c r="A855" t="inlineStr">
@@ -18388,6 +20952,9 @@
       <c r="E855" t="n">
         <v>1969.7846</v>
       </c>
+      <c r="F855" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="856">
       <c r="A856" t="inlineStr">
@@ -18409,6 +20976,9 @@
       <c r="E856" t="n">
         <v>2912.9214</v>
       </c>
+      <c r="F856" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="857">
       <c r="A857" t="inlineStr">
@@ -18430,6 +21000,9 @@
       <c r="E857" t="n">
         <v>2310.0343</v>
       </c>
+      <c r="F857" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="858">
       <c r="A858" t="inlineStr">
@@ -18451,6 +21024,9 @@
       <c r="E858" t="n">
         <v>2644.9217</v>
       </c>
+      <c r="F858" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="859">
       <c r="A859" t="inlineStr">
@@ -18472,6 +21048,9 @@
       <c r="E859" t="n">
         <v>2646.1437</v>
       </c>
+      <c r="F859" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="860">
       <c r="A860" t="inlineStr">
@@ -18493,6 +21072,9 @@
       <c r="E860" t="n">
         <v>2749.2098</v>
       </c>
+      <c r="F860" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="861">
       <c r="A861" t="inlineStr">
@@ -18514,6 +21096,9 @@
       <c r="E861" t="n">
         <v>2867.6492</v>
       </c>
+      <c r="F861" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="862">
       <c r="A862" t="inlineStr">
@@ -18535,6 +21120,9 @@
       <c r="E862" t="n">
         <v>2582.787</v>
       </c>
+      <c r="F862" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="863">
       <c r="A863" t="inlineStr">
@@ -18556,6 +21144,9 @@
       <c r="E863" t="n">
         <v>3872.6542</v>
       </c>
+      <c r="F863" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="864">
       <c r="A864" t="inlineStr">
@@ -18577,6 +21168,9 @@
       <c r="E864" t="n">
         <v>3873.6542</v>
       </c>
+      <c r="F864" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="865">
       <c r="A865" t="inlineStr">
@@ -18598,6 +21192,9 @@
       <c r="E865" t="n">
         <v>4020.6902</v>
       </c>
+      <c r="F865" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="866">
       <c r="A866" t="inlineStr">
@@ -18619,6 +21216,9 @@
       <c r="E866" t="n">
         <v>3324.2491</v>
       </c>
+      <c r="F866" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="867">
       <c r="A867" t="inlineStr">
@@ -18640,6 +21240,9 @@
       <c r="E867" t="n">
         <v>3255.3843</v>
       </c>
+      <c r="F867" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="868">
       <c r="A868" t="inlineStr">
@@ -18661,6 +21264,9 @@
       <c r="E868" t="n">
         <v>3468.3346</v>
       </c>
+      <c r="F868" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="869">
       <c r="A869" t="inlineStr">
@@ -18682,6 +21288,9 @@
       <c r="E869" t="n">
         <v>4633.9331</v>
       </c>
+      <c r="F869" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="870">
       <c r="A870" t="inlineStr">
@@ -18703,6 +21312,9 @@
       <c r="E870" t="n">
         <v>3391.5644</v>
       </c>
+      <c r="F870" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="871">
       <c r="A871" t="inlineStr">
@@ -18724,6 +21336,9 @@
       <c r="E871" t="n">
         <v>3417.5822</v>
       </c>
+      <c r="F871" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="872">
       <c r="A872" t="inlineStr">
@@ -18745,6 +21360,9 @@
       <c r="E872" t="n">
         <v>4642.7144</v>
       </c>
+      <c r="F872" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="873">
       <c r="A873" t="inlineStr">
@@ -18766,6 +21384,9 @@
       <c r="E873" t="n">
         <v>2741.2669</v>
       </c>
+      <c r="F873" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="874">
       <c r="A874" t="inlineStr">
@@ -18787,6 +21408,9 @@
       <c r="E874" t="n">
         <v>3166.25</v>
       </c>
+      <c r="F874" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="875">
       <c r="A875" t="inlineStr">
@@ -18808,6 +21432,9 @@
       <c r="E875" t="n">
         <v>2209.9727</v>
       </c>
+      <c r="F875" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="876">
       <c r="A876" t="inlineStr">
@@ -18829,6 +21456,9 @@
       <c r="E876" t="n">
         <v>2284.2186</v>
       </c>
+      <c r="F876" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="877">
       <c r="A877" t="inlineStr">
@@ -18850,6 +21480,9 @@
       <c r="E877" t="n">
         <v>2934.2186</v>
       </c>
+      <c r="F877" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="878">
       <c r="A878" t="inlineStr">
@@ -18871,6 +21504,9 @@
       <c r="E878" t="n">
         <v>3084.9727</v>
       </c>
+      <c r="F878" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="879">
       <c r="A879" t="inlineStr">
@@ -18892,6 +21528,9 @@
       <c r="E879" t="n">
         <v>2686.0858</v>
       </c>
+      <c r="F879" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="880">
       <c r="A880" t="inlineStr">
@@ -18913,6 +21552,9 @@
       <c r="E880" t="n">
         <v>2985.5384</v>
       </c>
+      <c r="F880" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="881">
       <c r="A881" t="inlineStr">
@@ -18934,6 +21576,9 @@
       <c r="E881" t="n">
         <v>2783.8509</v>
       </c>
+      <c r="F881" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="882">
       <c r="A882" t="inlineStr">
@@ -18955,6 +21600,9 @@
       <c r="E882" t="n">
         <v>3025.0971</v>
       </c>
+      <c r="F882" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="883">
       <c r="A883" t="inlineStr">
@@ -18976,6 +21624,9 @@
       <c r="E883" t="n">
         <v>2997.5164</v>
       </c>
+      <c r="F883" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="884">
       <c r="A884" t="inlineStr">
@@ -18997,6 +21648,9 @@
       <c r="E884" t="n">
         <v>3997.8532</v>
       </c>
+      <c r="F884" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="885">
       <c r="A885" t="inlineStr">
@@ -19018,6 +21672,9 @@
       <c r="E885" t="n">
         <v>3367.6509</v>
       </c>
+      <c r="F885" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="886">
       <c r="A886" t="inlineStr">
@@ -19039,6 +21696,9 @@
       <c r="E886" t="n">
         <v>2758.0485</v>
       </c>
+      <c r="F886" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="887">
       <c r="A887" t="inlineStr">
@@ -19060,6 +21720,9 @@
       <c r="E887" t="n">
         <v>2838.0485</v>
       </c>
+      <c r="F887" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="888">
       <c r="A888" t="inlineStr">
@@ -19081,6 +21744,9 @@
       <c r="E888" t="n">
         <v>2621.301</v>
       </c>
+      <c r="F888" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="889">
       <c r="A889" t="inlineStr">
@@ -19102,6 +21768,9 @@
       <c r="E889" t="n">
         <v>2608.2963</v>
       </c>
+      <c r="F889" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="890">
       <c r="A890" t="inlineStr">
@@ -19123,6 +21792,9 @@
       <c r="E890" t="n">
         <v>1137.8512</v>
       </c>
+      <c r="F890" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="891">
       <c r="A891" t="inlineStr">
@@ -19144,6 +21816,9 @@
       <c r="E891" t="n">
         <v>2172.461</v>
       </c>
+      <c r="F891" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="892">
       <c r="A892" t="inlineStr">
@@ -19165,6 +21840,9 @@
       <c r="E892" t="n">
         <v>4081.8158</v>
       </c>
+      <c r="F892" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="893">
       <c r="A893" t="inlineStr">
@@ -19186,6 +21864,9 @@
       <c r="E893" t="n">
         <v>3361.3037</v>
       </c>
+      <c r="F893" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="894">
       <c r="A894" t="inlineStr">
@@ -19207,6 +21888,9 @@
       <c r="E894" t="n">
         <v>3283.5647</v>
       </c>
+      <c r="F894" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="895">
       <c r="A895" t="inlineStr">
@@ -19228,6 +21912,9 @@
       <c r="E895" t="n">
         <v>2812.9413</v>
       </c>
+      <c r="F895" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="896">
       <c r="A896" t="inlineStr">
@@ -19249,6 +21936,9 @@
       <c r="E896" t="n">
         <v>3635.4032</v>
       </c>
+      <c r="F896" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="897">
       <c r="A897" t="inlineStr">
@@ -19270,6 +21960,9 @@
       <c r="E897" t="n">
         <v>1740.4948</v>
       </c>
+      <c r="F897" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="898">
       <c r="A898" t="inlineStr">
@@ -19291,6 +21984,9 @@
       <c r="E898" t="n">
         <v>5508.8298</v>
       </c>
+      <c r="F898" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="899">
       <c r="A899" t="inlineStr">
@@ -19312,6 +22008,9 @@
       <c r="E899" t="n">
         <v>2020.9095</v>
       </c>
+      <c r="F899" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="900">
       <c r="A900" t="inlineStr">
@@ -19333,6 +22032,9 @@
       <c r="E900" t="n">
         <v>1860.9</v>
       </c>
+      <c r="F900" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="901">
       <c r="A901" t="inlineStr">
@@ -19354,6 +22056,9 @@
       <c r="E901" t="n">
         <v>1915.6374</v>
       </c>
+      <c r="F901" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="902">
       <c r="A902" t="inlineStr">
@@ -19375,6 +22080,9 @@
       <c r="E902" t="n">
         <v>1859.9</v>
       </c>
+      <c r="F902" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="903">
       <c r="A903" t="inlineStr">
@@ -19396,6 +22104,9 @@
       <c r="E903" t="n">
         <v>2084.9</v>
       </c>
+      <c r="F903" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="904">
       <c r="A904" t="inlineStr">
@@ -19417,6 +22128,9 @@
       <c r="E904" t="n">
         <v>2009.9</v>
       </c>
+      <c r="F904" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="905">
       <c r="A905" t="inlineStr">
@@ -19438,6 +22152,9 @@
       <c r="E905" t="n">
         <v>2114.1085</v>
       </c>
+      <c r="F905" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="906">
       <c r="A906" t="inlineStr">
@@ -19459,6 +22176,9 @@
       <c r="E906" t="n">
         <v>1873.052</v>
       </c>
+      <c r="F906" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="907">
       <c r="A907" t="inlineStr">
@@ -19480,6 +22200,9 @@
       <c r="E907" t="n">
         <v>1118.48</v>
       </c>
+      <c r="F907" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="908">
       <c r="A908" t="inlineStr">
@@ -19501,6 +22224,9 @@
       <c r="E908" t="n">
         <v>1206.5333</v>
       </c>
+      <c r="F908" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="909">
       <c r="A909" t="inlineStr">
@@ -19522,6 +22248,9 @@
       <c r="E909" t="n">
         <v>1268.48</v>
       </c>
+      <c r="F909" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="910">
       <c r="A910" t="inlineStr">
@@ -19543,6 +22272,9 @@
       <c r="E910" t="n">
         <v>1969.0156</v>
       </c>
+      <c r="F910" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="911">
       <c r="A911" t="inlineStr">
@@ -19564,6 +22296,9 @@
       <c r="E911" t="n">
         <v>1806.9637</v>
       </c>
+      <c r="F911" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="912">
       <c r="A912" t="inlineStr">
@@ -19585,6 +22320,9 @@
       <c r="E912" t="n">
         <v>981.5333000000001</v>
       </c>
+      <c r="F912" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="913">
       <c r="A913" t="inlineStr">
@@ -19606,6 +22344,9 @@
       <c r="E913" t="n">
         <v>2077.7583</v>
       </c>
+      <c r="F913" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="914">
       <c r="A914" t="inlineStr">
@@ -19627,6 +22368,9 @@
       <c r="E914" t="n">
         <v>1193.48</v>
       </c>
+      <c r="F914" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="915">
       <c r="A915" t="inlineStr">
@@ -19648,6 +22392,9 @@
       <c r="E915" t="n">
         <v>1967.4091</v>
       </c>
+      <c r="F915" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="916">
       <c r="A916" t="inlineStr">
@@ -19669,6 +22416,9 @@
       <c r="E916" t="n">
         <v>1978.4089</v>
       </c>
+      <c r="F916" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="917">
       <c r="A917" t="inlineStr">
@@ -19690,6 +22440,9 @@
       <c r="E917" t="n">
         <v>3100.7268</v>
       </c>
+      <c r="F917" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="918">
       <c r="A918" t="inlineStr">
@@ -19711,6 +22464,9 @@
       <c r="E918" t="n">
         <v>3208.26</v>
       </c>
+      <c r="F918" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="919">
       <c r="A919" t="inlineStr">
@@ -19732,6 +22488,9 @@
       <c r="E919" t="n">
         <v>3113.48</v>
       </c>
+      <c r="F919" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="920">
       <c r="A920" t="inlineStr">
@@ -19753,6 +22512,9 @@
       <c r="E920" t="n">
         <v>4457.3146</v>
       </c>
+      <c r="F920" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="921">
       <c r="A921" t="inlineStr">
@@ -19774,6 +22536,9 @@
       <c r="E921" t="n">
         <v>2524.3637</v>
       </c>
+      <c r="F921" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="922">
       <c r="A922" t="inlineStr">
@@ -19795,6 +22560,9 @@
       <c r="E922" t="n">
         <v>2498.8</v>
       </c>
+      <c r="F922" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="923">
       <c r="A923" t="inlineStr">
@@ -19816,6 +22584,9 @@
       <c r="E923" t="n">
         <v>2498.8</v>
       </c>
+      <c r="F923" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="924">
       <c r="A924" t="inlineStr">
@@ -19837,6 +22608,9 @@
       <c r="E924" t="n">
         <v>2293.3472</v>
       </c>
+      <c r="F924" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="925">
       <c r="A925" t="inlineStr">
@@ -19858,6 +22632,9 @@
       <c r="E925" t="n">
         <v>1917.45</v>
       </c>
+      <c r="F925" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="926">
       <c r="A926" t="inlineStr">
@@ -19879,6 +22656,9 @@
       <c r="E926" t="n">
         <v>1526.4948</v>
       </c>
+      <c r="F926" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="927">
       <c r="A927" t="inlineStr">
@@ -19900,6 +22680,9 @@
       <c r="E927" t="n">
         <v>1932.8641</v>
       </c>
+      <c r="F927" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="928">
       <c r="A928" t="inlineStr">
@@ -19921,6 +22704,9 @@
       <c r="E928" t="n">
         <v>1666.3728</v>
       </c>
+      <c r="F928" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="929">
       <c r="A929" t="inlineStr">
@@ -19942,6 +22728,9 @@
       <c r="E929" t="n">
         <v>1879.9323</v>
       </c>
+      <c r="F929" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="930">
       <c r="A930" t="inlineStr">
@@ -19963,6 +22752,9 @@
       <c r="E930" t="n">
         <v>1879.9321</v>
       </c>
+      <c r="F930" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="931">
       <c r="A931" t="inlineStr">
@@ -19984,6 +22776,9 @@
       <c r="E931" t="n">
         <v>1900.1248</v>
       </c>
+      <c r="F931" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="932">
       <c r="A932" t="inlineStr">
@@ -20005,6 +22800,9 @@
       <c r="E932" t="n">
         <v>2473.2656</v>
       </c>
+      <c r="F932" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="933">
       <c r="A933" t="inlineStr">
@@ -20026,6 +22824,9 @@
       <c r="E933" t="n">
         <v>2500.8819</v>
       </c>
+      <c r="F933" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="934">
       <c r="A934" t="inlineStr">
@@ -20047,6 +22848,9 @@
       <c r="E934" t="n">
         <v>2579.0795</v>
       </c>
+      <c r="F934" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="935">
       <c r="A935" t="inlineStr">
@@ -20068,6 +22872,9 @@
       <c r="E935" t="n">
         <v>2650.6295</v>
       </c>
+      <c r="F935" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="936">
       <c r="A936" t="inlineStr">
@@ -20089,6 +22896,9 @@
       <c r="E936" t="n">
         <v>1662.87</v>
       </c>
+      <c r="F936" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="937">
       <c r="A937" t="inlineStr">
@@ -20110,6 +22920,9 @@
       <c r="E937" t="n">
         <v>1338.087</v>
       </c>
+      <c r="F937" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="938">
       <c r="A938" t="inlineStr">
@@ -20131,6 +22944,9 @@
       <c r="E938" t="n">
         <v>3022.8156</v>
       </c>
+      <c r="F938" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="939">
       <c r="A939" t="inlineStr">
@@ -20152,6 +22968,9 @@
       <c r="E939" t="n">
         <v>2196.7528</v>
       </c>
+      <c r="F939" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="940">
       <c r="A940" t="inlineStr">
@@ -20173,6 +22992,9 @@
       <c r="E940" t="n">
         <v>2648.3054</v>
       </c>
+      <c r="F940" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="941">
       <c r="A941" t="inlineStr">
@@ -20194,6 +23016,9 @@
       <c r="E941" t="n">
         <v>1117.45</v>
       </c>
+      <c r="F941" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="942">
       <c r="A942" t="inlineStr">
@@ -20215,6 +23040,9 @@
       <c r="E942" t="n">
         <v>1042.45</v>
       </c>
+      <c r="F942" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="943">
       <c r="A943" t="inlineStr">
@@ -20236,6 +23064,9 @@
       <c r="E943" t="n">
         <v>1117.45</v>
       </c>
+      <c r="F943" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="944">
       <c r="A944" t="inlineStr">
@@ -20257,6 +23088,9 @@
       <c r="E944" t="n">
         <v>1117.45</v>
       </c>
+      <c r="F944" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="945">
       <c r="A945" t="inlineStr">
@@ -20278,6 +23112,9 @@
       <c r="E945" t="n">
         <v>1200.0241</v>
       </c>
+      <c r="F945" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="946">
       <c r="A946" t="inlineStr">
@@ -20299,6 +23136,9 @@
       <c r="E946" t="n">
         <v>1192.45</v>
       </c>
+      <c r="F946" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="947">
       <c r="A947" t="inlineStr">
@@ -20320,6 +23160,9 @@
       <c r="E947" t="n">
         <v>2424.3345</v>
       </c>
+      <c r="F947" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="948">
       <c r="A948" t="inlineStr">
@@ -20341,6 +23184,9 @@
       <c r="E948" t="n">
         <v>1042.45</v>
       </c>
+      <c r="F948" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="949">
       <c r="A949" t="inlineStr">
@@ -20362,6 +23208,9 @@
       <c r="E949" t="n">
         <v>1117.45</v>
       </c>
+      <c r="F949" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="950">
       <c r="A950" t="inlineStr">
@@ -20383,6 +23232,9 @@
       <c r="E950" t="n">
         <v>1042.45</v>
       </c>
+      <c r="F950" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="951">
       <c r="A951" t="inlineStr">
@@ -20404,6 +23256,9 @@
       <c r="E951" t="n">
         <v>1199.6198</v>
       </c>
+      <c r="F951" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="952">
       <c r="A952" t="inlineStr">
@@ -20425,6 +23280,9 @@
       <c r="E952" t="n">
         <v>994.3870000000001</v>
       </c>
+      <c r="F952" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="953">
       <c r="A953" t="inlineStr">
@@ -20446,6 +23304,9 @@
       <c r="E953" t="n">
         <v>2498.8</v>
       </c>
+      <c r="F953" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="954">
       <c r="A954" t="inlineStr">
@@ -20467,6 +23328,9 @@
       <c r="E954" t="n">
         <v>1186.4774</v>
       </c>
+      <c r="F954" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="955">
       <c r="A955" t="inlineStr">
@@ -20488,6 +23352,9 @@
       <c r="E955" t="n">
         <v>3044.7255</v>
       </c>
+      <c r="F955" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="956">
       <c r="A956" t="inlineStr">
@@ -20509,6 +23376,9 @@
       <c r="E956" t="n">
         <v>75</v>
       </c>
+      <c r="F956" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="957">
       <c r="A957" t="inlineStr">
@@ -20530,6 +23400,9 @@
       <c r="E957" t="n">
         <v>2359.0021</v>
       </c>
+      <c r="F957" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="958">
       <c r="A958" t="inlineStr">
@@ -20551,6 +23424,9 @@
       <c r="E958" t="n">
         <v>1066.6667</v>
       </c>
+      <c r="F958" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="959">
       <c r="A959" t="inlineStr">
@@ -20572,6 +23448,9 @@
       <c r="E959" t="n">
         <v>4058.3343</v>
       </c>
+      <c r="F959" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="960">
       <c r="A960" t="inlineStr">
@@ -20593,6 +23472,9 @@
       <c r="E960" t="n">
         <v>2368.6496</v>
       </c>
+      <c r="F960" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="961">
       <c r="A961" t="inlineStr">
@@ -20614,6 +23496,9 @@
       <c r="E961" t="n">
         <v>3018.3458</v>
       </c>
+      <c r="F961" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="962">
       <c r="A962" t="inlineStr">
@@ -20635,6 +23520,9 @@
       <c r="E962" t="n">
         <v>3247.5768</v>
       </c>
+      <c r="F962" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="963">
       <c r="A963" t="inlineStr">
@@ -20656,6 +23544,9 @@
       <c r="E963" t="n">
         <v>3282.5991</v>
       </c>
+      <c r="F963" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="964">
       <c r="A964" t="inlineStr">
@@ -20677,6 +23568,9 @@
       <c r="E964" t="n">
         <v>1738.4</v>
       </c>
+      <c r="F964" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="965">
       <c r="A965" t="inlineStr">
@@ -20698,6 +23592,9 @@
       <c r="E965" t="n">
         <v>2488.5379</v>
       </c>
+      <c r="F965" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="966">
       <c r="A966" t="inlineStr">
@@ -20719,6 +23616,9 @@
       <c r="E966" t="n">
         <v>2409.7682</v>
       </c>
+      <c r="F966" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="967">
       <c r="A967" t="inlineStr">
@@ -20740,6 +23640,9 @@
       <c r="E967" t="n">
         <v>2352.8837</v>
       </c>
+      <c r="F967" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="968">
       <c r="A968" t="inlineStr">
@@ -20761,6 +23664,9 @@
       <c r="E968" t="n">
         <v>2351.8837</v>
       </c>
+      <c r="F968" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="969">
       <c r="A969" t="inlineStr">
@@ -20782,6 +23688,9 @@
       <c r="E969" t="n">
         <v>1958.9925</v>
       </c>
+      <c r="F969" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="970">
       <c r="A970" t="inlineStr">
@@ -20803,6 +23712,9 @@
       <c r="E970" t="n">
         <v>2247.3267</v>
       </c>
+      <c r="F970" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="971">
       <c r="A971" t="inlineStr">
@@ -20824,6 +23736,9 @@
       <c r="E971" t="n">
         <v>2262.1451</v>
       </c>
+      <c r="F971" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="972">
       <c r="A972" t="inlineStr">
@@ -20845,6 +23760,9 @@
       <c r="E972" t="n">
         <v>2401.2795</v>
       </c>
+      <c r="F972" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="973">
       <c r="A973" t="inlineStr">
@@ -20866,6 +23784,9 @@
       <c r="E973" t="n">
         <v>2035.7567</v>
       </c>
+      <c r="F973" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="974">
       <c r="A974" t="inlineStr">
@@ -20887,6 +23808,9 @@
       <c r="E974" t="n">
         <v>2780.1978</v>
       </c>
+      <c r="F974" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="975">
       <c r="A975" t="inlineStr">
@@ -20908,6 +23832,9 @@
       <c r="E975" t="n">
         <v>1803.3536</v>
       </c>
+      <c r="F975" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="976">
       <c r="A976" t="inlineStr">
@@ -20929,6 +23856,9 @@
       <c r="E976" t="n">
         <v>2031.6994</v>
       </c>
+      <c r="F976" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="977">
       <c r="A977" t="inlineStr">
@@ -20950,6 +23880,9 @@
       <c r="E977" t="n">
         <v>2503.0869</v>
       </c>
+      <c r="F977" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="978">
       <c r="A978" t="inlineStr">
@@ -20971,6 +23904,9 @@
       <c r="E978" t="n">
         <v>2456.1633</v>
       </c>
+      <c r="F978" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="979">
       <c r="A979" t="inlineStr">
@@ -20992,6 +23928,9 @@
       <c r="E979" t="n">
         <v>2459.1637</v>
       </c>
+      <c r="F979" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="980">
       <c r="A980" t="inlineStr">
@@ -21013,6 +23952,9 @@
       <c r="E980" t="n">
         <v>1843.7656</v>
       </c>
+      <c r="F980" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="981">
       <c r="A981" t="inlineStr">
@@ -21034,6 +23976,9 @@
       <c r="E981" t="n">
         <v>3858.5356</v>
       </c>
+      <c r="F981" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="982">
       <c r="A982" t="inlineStr">
@@ -21055,6 +24000,9 @@
       <c r="E982" t="n">
         <v>3522.0528</v>
       </c>
+      <c r="F982" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="983">
       <c r="A983" t="inlineStr">
@@ -21076,6 +24024,9 @@
       <c r="E983" t="n">
         <v>2173.8483</v>
       </c>
+      <c r="F983" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="984">
       <c r="A984" t="inlineStr">
@@ -21097,6 +24048,9 @@
       <c r="E984" t="n">
         <v>3451.8841</v>
       </c>
+      <c r="F984" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="985">
       <c r="A985" t="inlineStr">
@@ -21117,6 +24071,9 @@
       </c>
       <c r="E985" t="n">
         <v>3582.0678</v>
+      </c>
+      <c r="F985" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
